--- a/files/九龙-启德-Monaco Marine.xlsx
+++ b/files/九龙-启德-Monaco Marine.xlsx
@@ -9539,7 +9539,7 @@
       </c>
       <c r="G195" s="3" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="H195" s="5" t="n">
@@ -28278,7 +28278,7 @@
           <t>F | 440呎 (2房)
 $1,083万
 $24,607/呎
-(26年-05月)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="H30" s="16" t="inlineStr">

--- a/files/九龙-启德-Monaco Marine.xlsx
+++ b/files/九龙-启德-Monaco Marine.xlsx
@@ -8,12 +8,12 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1A座 销控表" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1B座 销控表" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="低座A 销控表" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="低座B 销控表" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="低座C 销控表" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="低座D 销控表" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1A座" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1B座" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="低座A" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="低座B" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="低座C" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="低座D" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -25,7 +25,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -49,14 +49,19 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
-      <color rgb="007F7F7F"/>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00000000"/>
       <sz val="9"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
       <b val="1"/>
-      <color rgb="007F7F7F"/>
-      <sz val="11"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
@@ -68,7 +73,7 @@
       <name val="Microsoft YaHei"/>
       <b val="1"/>
       <color rgb="00004D00"/>
-      <sz val="11"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
@@ -79,7 +84,7 @@
       <name val="Microsoft YaHei"/>
       <b val="1"/>
       <color rgb="00002060"/>
-      <sz val="11"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
@@ -90,7 +95,7 @@
       <name val="Microsoft YaHei"/>
       <b val="1"/>
       <color rgb="00660000"/>
-      <sz val="11"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
@@ -100,9 +105,30 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
       <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="11"/>
+      <color rgb="007F7F7F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="8"/>
     </font>
   </fonts>
   <fills count="9">
@@ -150,8 +176,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E5E5E5"/>
-        <bgColor rgb="00E5E5E5"/>
+        <fgColor rgb="00E8E8E8"/>
+        <bgColor rgb="00E8E8E8"/>
       </patternFill>
     </fill>
   </fills>
@@ -181,7 +207,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -198,19 +224,7 @@
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -228,13 +242,37 @@
     <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -612,7 +650,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -26405,179 +26443,179 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I36"/>
+  <dimension ref="A1:I35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Monaco Marine - 1A座 销控网格图</t>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>1A座 销控网格图</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>总套数</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="8" t="inlineStr">
         <is>
           <t>在售 (Sale)</t>
         </is>
       </c>
-      <c r="C2" s="8" t="inlineStr">
+      <c r="C2" s="9" t="inlineStr">
         <is>
           <t>已定价未售</t>
         </is>
       </c>
-      <c r="D2" s="9" t="inlineStr">
+      <c r="D2" s="10" t="inlineStr">
         <is>
           <t>已售 (Sold)</t>
         </is>
       </c>
-      <c r="E2" s="10" t="inlineStr">
+      <c r="E2" s="11" t="inlineStr">
         <is>
           <t>暂停销售</t>
         </is>
       </c>
-      <c r="F2" s="6" t="inlineStr">
+      <c r="F2" s="12" t="inlineStr">
         <is>
           <t>待售 (Pending)</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>240 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>3 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>237 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>237</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C4" s="19" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D4" s="19" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E4" s="19" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F4" s="19" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G4" s="19" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H4" s="19" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="I4" s="19" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>38/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
         <is>
           <t>A | 1708呎 (4+房)
-$6,960万
+$6960万
 $40,749/呎
 (24年-02月)</t>
         </is>
       </c>
-      <c r="C6" s="17" t="inlineStr"/>
-      <c r="D6" s="17" t="inlineStr"/>
-      <c r="E6" s="16" t="inlineStr">
+      <c r="C5" s="21" t="inlineStr"/>
+      <c r="D5" s="21" t="inlineStr"/>
+      <c r="E5" s="20" t="inlineStr">
         <is>
           <t>D | 442呎 (2房)
-$1,138万
+$1138万
 $25,735/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F6" s="16" t="inlineStr">
+      <c r="F5" s="20" t="inlineStr">
         <is>
           <t>E | 437呎 (2房)
-$1,170万
+$1170万
 $26,773/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G6" s="16" t="inlineStr">
+      <c r="G5" s="20" t="inlineStr">
         <is>
           <t>F | 440呎 (2房)
-$1,178万
+$1178万
 $26,775/呎
 (已售)</t>
         </is>
       </c>
-      <c r="H6" s="16" t="inlineStr">
+      <c r="H5" s="20" t="inlineStr">
         <is>
           <t>G | 326呎 (1房)
 $868万
@@ -26585,7 +26623,7 @@
 (25年-01月)</t>
         </is>
       </c>
-      <c r="I6" s="18" t="inlineStr">
+      <c r="I5" s="22" t="inlineStr">
         <is>
           <t>H | 328呎 (1房)
 $989万
@@ -26594,21 +26632,21 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>37/F</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
         <is>
           <t>A | 713呎 (3房)
-$2,099万
+$2099万
 $29,433/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C7" s="16" t="inlineStr">
+      <c r="C6" s="20" t="inlineStr">
         <is>
           <t>B | 326呎 (1房)
 $955万
@@ -26616,39 +26654,39 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D7" s="16" t="inlineStr">
+      <c r="D6" s="20" t="inlineStr">
         <is>
           <t>C | 617呎 (3房)
-$1,813万
+$1813万
 $29,387/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E7" s="16" t="inlineStr">
+      <c r="E6" s="20" t="inlineStr">
         <is>
           <t>D | 443呎 (2房)
-$1,168万
+$1168万
 $26,363/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F7" s="16" t="inlineStr">
+      <c r="F6" s="20" t="inlineStr">
         <is>
           <t>E | 438呎 (2房)
-$1,166万
+$1166万
 $26,616/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G7" s="16" t="inlineStr">
+      <c r="G6" s="20" t="inlineStr">
         <is>
           <t>F | 440呎 (2房)
-$1,171万
+$1171万
 $26,616/呎
 (已售)</t>
         </is>
       </c>
-      <c r="H7" s="16" t="inlineStr">
+      <c r="H6" s="20" t="inlineStr">
         <is>
           <t>G | 326呎 (1房)
 $891万
@@ -26656,7 +26694,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I7" s="16" t="inlineStr">
+      <c r="I6" s="20" t="inlineStr">
         <is>
           <t>H | 327呎 (1房)
 $899万
@@ -26665,21 +26703,21 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>36/F</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="inlineStr">
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
         <is>
           <t>A | 713呎 (3房)
-$2,034万
+$2034万
 $28,534/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C8" s="16" t="inlineStr">
+      <c r="C7" s="20" t="inlineStr">
         <is>
           <t>B | 326呎 (1房)
 $958万
@@ -26687,39 +26725,39 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D8" s="16" t="inlineStr">
+      <c r="D7" s="20" t="inlineStr">
         <is>
           <t>C | 616呎 (3房)
-$1,808万
+$1808万
 $29,347/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E8" s="16" t="inlineStr">
+      <c r="E7" s="20" t="inlineStr">
         <is>
           <t>D | 443呎 (2房)
-$1,133万
+$1133万
 $25,582/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F8" s="16" t="inlineStr">
+      <c r="F7" s="20" t="inlineStr">
         <is>
           <t>E | 438呎 (2房)
-$1,162万
+$1162万
 $26,537/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G8" s="16" t="inlineStr">
+      <c r="G7" s="20" t="inlineStr">
         <is>
           <t>F | 440呎 (2房)
-$1,168万
+$1168万
 $26,536/呎
 (已售)</t>
         </is>
       </c>
-      <c r="H8" s="16" t="inlineStr">
+      <c r="H7" s="20" t="inlineStr">
         <is>
           <t>G | 326呎 (1房)
 $889万
@@ -26727,7 +26765,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I8" s="16" t="inlineStr">
+      <c r="I7" s="20" t="inlineStr">
         <is>
           <t>H | 327呎 (1房)
 $878万
@@ -26736,21 +26774,21 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>35/F</t>
-        </is>
-      </c>
-      <c r="B9" s="16" t="inlineStr">
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
         <is>
           <t>A | 713呎 (3房)
-$2,086万
+$2086万
 $29,258/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C9" s="16" t="inlineStr">
+      <c r="C8" s="20" t="inlineStr">
         <is>
           <t>B | 326呎 (1房)
 $960万
@@ -26758,39 +26796,39 @@
 (24年-04月)</t>
         </is>
       </c>
-      <c r="D9" s="16" t="inlineStr">
+      <c r="D8" s="20" t="inlineStr">
         <is>
           <t>C | 616呎 (3房)
-$1,753万
+$1753万
 $28,451/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E9" s="16" t="inlineStr">
+      <c r="E8" s="20" t="inlineStr">
         <is>
           <t>D | 443呎 (2房)
-$1,163万
+$1163万
 $26,257/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F9" s="16" t="inlineStr">
+      <c r="F8" s="20" t="inlineStr">
         <is>
           <t>E | 438呎 (2房)
-$1,159万
+$1159万
 $26,457/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G9" s="16" t="inlineStr">
+      <c r="G8" s="20" t="inlineStr">
         <is>
           <t>F | 440呎 (2房)
-$1,164万
+$1164万
 $26,457/呎
 (已售)</t>
         </is>
       </c>
-      <c r="H9" s="16" t="inlineStr">
+      <c r="H8" s="20" t="inlineStr">
         <is>
           <t>G | 326呎 (1房)
 $893万
@@ -26798,7 +26836,7 @@
 (26年-05月)</t>
         </is>
       </c>
-      <c r="I9" s="16" t="inlineStr">
+      <c r="I8" s="20" t="inlineStr">
         <is>
           <t>H | 328呎 (1房)
 $897万
@@ -26807,21 +26845,21 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>33/F</t>
-        </is>
-      </c>
-      <c r="B10" s="16" t="inlineStr">
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
         <is>
           <t>A | 713呎 (3房)
-$2,022万
+$2022万
 $28,365/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C10" s="16" t="inlineStr">
+      <c r="C9" s="20" t="inlineStr">
         <is>
           <t>B | 326呎 (1房)
 $946万
@@ -26829,39 +26867,39 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D10" s="16" t="inlineStr">
+      <c r="D9" s="20" t="inlineStr">
         <is>
           <t>C | 616呎 (3房)
-$1,747万
+$1747万
 $28,367/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E10" s="16" t="inlineStr">
+      <c r="E9" s="20" t="inlineStr">
         <is>
           <t>D | 443呎 (2房)
-$1,129万
+$1129万
 $25,479/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F10" s="16" t="inlineStr">
+      <c r="F9" s="20" t="inlineStr">
         <is>
           <t>E | 438呎 (2房)
-$1,124万
+$1124万
 $25,651/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G10" s="16" t="inlineStr">
+      <c r="G9" s="20" t="inlineStr">
         <is>
           <t>F | 440呎 (2房)
-$1,161万
+$1161万
 $26,377/呎
 (24年-04月)</t>
         </is>
       </c>
-      <c r="H10" s="16" t="inlineStr">
+      <c r="H9" s="20" t="inlineStr">
         <is>
           <t>G | 326呎 (1房)
 $887万
@@ -26869,7 +26907,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I10" s="16" t="inlineStr">
+      <c r="I9" s="20" t="inlineStr">
         <is>
           <t>H | 327呎 (1房)
 $896万
@@ -26878,21 +26916,21 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>32/F</t>
-        </is>
-      </c>
-      <c r="B11" s="16" t="inlineStr">
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
         <is>
           <t>A | 713呎 (3房)
-$2,074万
+$2074万
 $29,083/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C11" s="16" t="inlineStr">
+      <c r="C10" s="20" t="inlineStr">
         <is>
           <t>B | 326呎 (1房)
 $954万
@@ -26900,39 +26938,39 @@
 (25年-01月)</t>
         </is>
       </c>
-      <c r="D11" s="16" t="inlineStr">
+      <c r="D10" s="20" t="inlineStr">
         <is>
           <t>C | 616呎 (3房)
-$1,792万
+$1792万
 $29,084/呎
 (22年-04月)</t>
         </is>
       </c>
-      <c r="E11" s="16" t="inlineStr">
+      <c r="E10" s="20" t="inlineStr">
         <is>
           <t>D | 443呎 (2房)
-$1,126万
+$1126万
 $25,429/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F11" s="16" t="inlineStr">
+      <c r="F10" s="20" t="inlineStr">
         <is>
           <t>E | 438呎 (2房)
-$1,152万
+$1152万
 $26,297/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G11" s="16" t="inlineStr">
+      <c r="G10" s="20" t="inlineStr">
         <is>
           <t>F | 440呎 (2房)
-$1,157万
+$1157万
 $26,298/呎
 (已售)</t>
         </is>
       </c>
-      <c r="H11" s="16" t="inlineStr">
+      <c r="H10" s="20" t="inlineStr">
         <is>
           <t>G | 326呎 (1房)
 $885万
@@ -26940,7 +26978,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I11" s="16" t="inlineStr">
+      <c r="I10" s="20" t="inlineStr">
         <is>
           <t>H | 328呎 (1房)
 $895万
@@ -26949,21 +26987,21 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>31/F</t>
-        </is>
-      </c>
-      <c r="B12" s="16" t="inlineStr">
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B11" s="20" t="inlineStr">
         <is>
           <t>A | 713呎 (3房)
-$2,067万
+$2067万
 $28,996/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C12" s="16" t="inlineStr">
+      <c r="C11" s="20" t="inlineStr">
         <is>
           <t>B | 326呎 (1房)
 $952万
@@ -26971,39 +27009,39 @@
 (25年-11月)</t>
         </is>
       </c>
-      <c r="D12" s="16" t="inlineStr">
+      <c r="D11" s="20" t="inlineStr">
         <is>
           <t>C | 617呎 (3房)
-$1,737万
+$1737万
 $28,151/呎
 (24年-04月)</t>
         </is>
       </c>
-      <c r="E12" s="16" t="inlineStr">
+      <c r="E11" s="20" t="inlineStr">
         <is>
           <t>D | 443呎 (2房)
-$1,156万
+$1156万
 $26,099/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F12" s="16" t="inlineStr">
+      <c r="F11" s="20" t="inlineStr">
         <is>
           <t>E | 438呎 (2房)
-$1,148万
+$1148万
 $26,219/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G12" s="16" t="inlineStr">
+      <c r="G11" s="20" t="inlineStr">
         <is>
           <t>F | 440呎 (2房)
-$1,122万
+$1122万
 $25,495/呎
 (已售)</t>
         </is>
       </c>
-      <c r="H12" s="16" t="inlineStr">
+      <c r="H11" s="20" t="inlineStr">
         <is>
           <t>G | 326呎 (1房)
 $860万
@@ -27011,7 +27049,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I12" s="16" t="inlineStr">
+      <c r="I11" s="20" t="inlineStr">
         <is>
           <t>H | 328呎 (1房)
 $894万
@@ -27020,21 +27058,21 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>30/F</t>
-        </is>
-      </c>
-      <c r="B13" s="16" t="inlineStr">
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="inlineStr">
         <is>
           <t>A | 714呎 (3房)
-$2,004万
+$2004万
 $28,070/呎
 (22年-04月)</t>
         </is>
       </c>
-      <c r="C13" s="16" t="inlineStr">
+      <c r="C12" s="20" t="inlineStr">
         <is>
           <t>B | 326呎 (1房)
 $949万
@@ -27042,39 +27080,39 @@
 (25年-09月)</t>
         </is>
       </c>
-      <c r="D13" s="16" t="inlineStr">
+      <c r="D12" s="20" t="inlineStr">
         <is>
           <t>C | 616呎 (3房)
-$1,728万
+$1728万
 $28,044/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E13" s="16" t="inlineStr">
+      <c r="E12" s="20" t="inlineStr">
         <is>
           <t>D | 443呎 (2房)
-$1,154万
+$1154万
 $26,047/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F13" s="16" t="inlineStr">
+      <c r="F12" s="20" t="inlineStr">
         <is>
           <t>E | 438呎 (2房)
-$1,145万
+$1145万
 $26,142/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G13" s="16" t="inlineStr">
+      <c r="G12" s="20" t="inlineStr">
         <is>
           <t>F | 440呎 (2房)
-$1,118万
+$1118万
 $25,418/呎
 (已售)</t>
         </is>
       </c>
-      <c r="H13" s="16" t="inlineStr">
+      <c r="H12" s="20" t="inlineStr">
         <is>
           <t>G | 326呎 (1房)
 $858万
@@ -27082,7 +27120,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I13" s="16" t="inlineStr">
+      <c r="I12" s="20" t="inlineStr">
         <is>
           <t>H | 327呎 (1房)
 $892万
@@ -27091,21 +27129,21 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>29/F</t>
-        </is>
-      </c>
-      <c r="B14" s="16" t="inlineStr">
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
         <is>
           <t>A | 714呎 (3房)
-$1,998万
+$1998万
 $27,987/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C14" s="16" t="inlineStr">
+      <c r="C13" s="20" t="inlineStr">
         <is>
           <t>B | 326呎 (1房)
 $946万
@@ -27113,39 +27151,39 @@
 (26年-01月)</t>
         </is>
       </c>
-      <c r="D14" s="16" t="inlineStr">
+      <c r="D13" s="20" t="inlineStr">
         <is>
           <t>C | 616呎 (3房)
-$1,771万
+$1771万
 $28,753/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E14" s="16" t="inlineStr">
+      <c r="E13" s="20" t="inlineStr">
         <is>
           <t>D | 443呎 (2房)
-$1,120万
+$1120万
 $25,278/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F14" s="16" t="inlineStr">
+      <c r="F13" s="20" t="inlineStr">
         <is>
           <t>E | 438呎 (2房)
-$1,110万
+$1110万
 $25,345/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G14" s="16" t="inlineStr">
+      <c r="G13" s="20" t="inlineStr">
         <is>
           <t>F | 440呎 (2房)
-$1,115万
+$1115万
 $25,343/呎
 (已售)</t>
         </is>
       </c>
-      <c r="H14" s="16" t="inlineStr">
+      <c r="H13" s="20" t="inlineStr">
         <is>
           <t>G | 326呎 (1房)
 $880万
@@ -27153,7 +27191,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I14" s="18" t="inlineStr">
+      <c r="I13" s="22" t="inlineStr">
         <is>
           <t>H | 328呎 (1房)
 $979万
@@ -27162,21 +27200,21 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>28/F</t>
-        </is>
-      </c>
-      <c r="B15" s="16" t="inlineStr">
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
         <is>
           <t>A | 713呎 (3房)
-$1,992万
+$1992万
 $27,942/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C15" s="16" t="inlineStr">
+      <c r="C14" s="20" t="inlineStr">
         <is>
           <t>B | 326呎 (1房)
 $957万
@@ -27184,39 +27222,39 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D15" s="16" t="inlineStr">
+      <c r="D14" s="20" t="inlineStr">
         <is>
           <t>C | 617呎 (3房)
-$1,766万
+$1766万
 $28,622/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E15" s="16" t="inlineStr">
+      <c r="E14" s="20" t="inlineStr">
         <is>
           <t>D | 443呎 (2房)
-$1,148万
+$1148万
 $25,916/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F15" s="16" t="inlineStr">
+      <c r="F14" s="20" t="inlineStr">
         <is>
           <t>E | 438呎 (2房)
-$1,107万
+$1107万
 $25,267/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G15" s="16" t="inlineStr">
+      <c r="G14" s="20" t="inlineStr">
         <is>
           <t>F | 440呎 (2房)
-$1,112万
+$1112万
 $25,268/呎
 (已售)</t>
         </is>
       </c>
-      <c r="H15" s="16" t="inlineStr">
+      <c r="H14" s="20" t="inlineStr">
         <is>
           <t>G | 326呎 (1房)
 $878万
@@ -27224,7 +27262,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I15" s="16" t="inlineStr">
+      <c r="I14" s="20" t="inlineStr">
         <is>
           <t>H | 327呎 (1房)
 $889万
@@ -27233,21 +27271,21 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>27/F</t>
-        </is>
-      </c>
-      <c r="B16" s="16" t="inlineStr">
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
         <is>
           <t>A | 713呎 (3房)
-$1,980万
+$1980万
 $27,776/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C16" s="16" t="inlineStr">
+      <c r="C15" s="20" t="inlineStr">
         <is>
           <t>B | 326呎 (1房)
 $940万
@@ -27255,39 +27293,39 @@
 (24年-06月)</t>
         </is>
       </c>
-      <c r="D16" s="16" t="inlineStr">
+      <c r="D15" s="20" t="inlineStr">
         <is>
           <t>C | 617呎 (3房)
-$1,755万
+$1755万
 $28,451/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E16" s="16" t="inlineStr">
+      <c r="E15" s="20" t="inlineStr">
         <is>
           <t>D | 443呎 (2房)
-$1,142万
+$1142万
 $25,788/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F16" s="16" t="inlineStr">
+      <c r="F15" s="20" t="inlineStr">
         <is>
           <t>E | 438呎 (2房)
-$1,130万
+$1130万
 $25,799/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G16" s="16" t="inlineStr">
+      <c r="G15" s="20" t="inlineStr">
         <is>
           <t>F | 440呎 (2房)
-$1,135万
+$1135万
 $25,800/呎
 (24年-06月)</t>
         </is>
       </c>
-      <c r="H16" s="16" t="inlineStr">
+      <c r="H15" s="20" t="inlineStr">
         <is>
           <t>G | 326呎 (1房)
 $852万
@@ -27295,7 +27333,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I16" s="16" t="inlineStr">
+      <c r="I15" s="20" t="inlineStr">
         <is>
           <t>H | 327呎 (1房)
 $868万
@@ -27304,21 +27342,21 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B17" s="16" t="inlineStr">
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
         <is>
           <t>A | 713呎 (3房)
-$2,031万
+$2031万
 $28,480/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C17" s="16" t="inlineStr">
+      <c r="C16" s="20" t="inlineStr">
         <is>
           <t>B | 326呎 (1房)
 $953万
@@ -27326,39 +27364,39 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D17" s="16" t="inlineStr">
+      <c r="D16" s="20" t="inlineStr">
         <is>
           <t>C | 616呎 (3房)
-$1,702万
+$1702万
 $27,627/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E17" s="16" t="inlineStr">
+      <c r="E16" s="20" t="inlineStr">
         <is>
           <t>D | 443呎 (2房)
-$1,140万
+$1140万
 $25,725/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F17" s="16" t="inlineStr">
+      <c r="F16" s="20" t="inlineStr">
         <is>
           <t>E | 438呎 (2房)
-$1,127万
+$1127万
 $25,724/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G17" s="16" t="inlineStr">
+      <c r="G16" s="20" t="inlineStr">
         <is>
           <t>F | 440呎 (2房)
-$1,132万
+$1132万
 $25,723/呎
 (已售)</t>
         </is>
       </c>
-      <c r="H17" s="16" t="inlineStr">
+      <c r="H16" s="20" t="inlineStr">
         <is>
           <t>G | 326呎 (1房)
 $874万
@@ -27366,7 +27404,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I17" s="16" t="inlineStr">
+      <c r="I16" s="20" t="inlineStr">
         <is>
           <t>H | 327呎 (1房)
 $866万
@@ -27375,21 +27413,21 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B18" s="16" t="inlineStr">
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B17" s="20" t="inlineStr">
         <is>
           <t>A | 713呎 (3房)
-$1,969万
+$1969万
 $27,610/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C18" s="16" t="inlineStr">
+      <c r="C17" s="20" t="inlineStr">
         <is>
           <t>B | 326呎 (1房)
 $948万
@@ -27397,39 +27435,39 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D18" s="16" t="inlineStr">
+      <c r="D17" s="20" t="inlineStr">
         <is>
           <t>C | 616呎 (3房)
-$1,745万
+$1745万
 $28,326/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E18" s="16" t="inlineStr">
+      <c r="E17" s="20" t="inlineStr">
         <is>
           <t>D | 443呎 (2房)
-$1,137万
+$1137万
 $25,659/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F18" s="16" t="inlineStr">
+      <c r="F17" s="20" t="inlineStr">
         <is>
           <t>E | 438呎 (2房)
-$1,123万
+$1123万
 $25,644/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G18" s="16" t="inlineStr">
+      <c r="G17" s="20" t="inlineStr">
         <is>
           <t>F | 440呎 (2房)
-$1,128万
+$1128万
 $25,645/呎
 (已售)</t>
         </is>
       </c>
-      <c r="H18" s="16" t="inlineStr">
+      <c r="H17" s="20" t="inlineStr">
         <is>
           <t>G | 326呎 (1房)
 $872万
@@ -27437,7 +27475,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I18" s="16" t="inlineStr">
+      <c r="I17" s="20" t="inlineStr">
         <is>
           <t>H | 327呎 (1房)
 $895万
@@ -27446,21 +27484,21 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B19" s="16" t="inlineStr">
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B18" s="20" t="inlineStr">
         <is>
           <t>A | 713呎 (3房)
-$1,963万
+$1963万
 $27,527/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C19" s="16" t="inlineStr">
+      <c r="C18" s="20" t="inlineStr">
         <is>
           <t>B | 326呎 (1房)
 $945万
@@ -27468,39 +27506,39 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D19" s="16" t="inlineStr">
+      <c r="D18" s="20" t="inlineStr">
         <is>
           <t>C | 617呎 (3房)
-$1,692万
+$1692万
 $27,418/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E19" s="16" t="inlineStr">
+      <c r="E18" s="20" t="inlineStr">
         <is>
           <t>D | 443呎 (2房)
-$1,103万
+$1103万
 $24,889/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F19" s="16" t="inlineStr">
+      <c r="F18" s="20" t="inlineStr">
         <is>
           <t>E | 438呎 (2房)
-$1,120万
+$1120万
 $25,568/呎
 (22年-04月)</t>
         </is>
       </c>
-      <c r="G19" s="16" t="inlineStr">
+      <c r="G18" s="20" t="inlineStr">
         <is>
           <t>F | 440呎 (2房)
-$1,125万
+$1125万
 $25,570/呎
 (已售)</t>
         </is>
       </c>
-      <c r="H19" s="16" t="inlineStr">
+      <c r="H18" s="20" t="inlineStr">
         <is>
           <t>G | 326呎 (1房)
 $870万
@@ -27508,7 +27546,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I19" s="16" t="inlineStr">
+      <c r="I18" s="20" t="inlineStr">
         <is>
           <t>H | 327呎 (1房)
 $881万
@@ -27517,21 +27555,21 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B20" s="16" t="inlineStr">
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B19" s="20" t="inlineStr">
         <is>
           <t>A | 713呎 (3房)
-$1,957万
+$1957万
 $27,445/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C20" s="16" t="inlineStr">
+      <c r="C19" s="20" t="inlineStr">
         <is>
           <t>B | 326呎 (1房)
 $944万
@@ -27539,39 +27577,39 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D20" s="16" t="inlineStr">
+      <c r="D19" s="20" t="inlineStr">
         <is>
           <t>C | 617呎 (3房)
-$1,734万
+$1734万
 $28,112/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E20" s="16" t="inlineStr">
+      <c r="E19" s="20" t="inlineStr">
         <is>
           <t>D | 443呎 (2房)
-$1,131万
+$1131万
 $25,533/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F20" s="16" t="inlineStr">
+      <c r="F19" s="20" t="inlineStr">
         <is>
           <t>E | 438呎 (2房)
-$1,116万
+$1116万
 $25,491/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G20" s="16" t="inlineStr">
+      <c r="G19" s="20" t="inlineStr">
         <is>
           <t>F | 440呎 (2房)
-$1,091万
+$1091万
 $24,789/呎
 (已售)</t>
         </is>
       </c>
-      <c r="H20" s="16" t="inlineStr">
+      <c r="H19" s="20" t="inlineStr">
         <is>
           <t>G | 326呎 (1房)
 $867万
@@ -27579,7 +27617,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I20" s="16" t="inlineStr">
+      <c r="I19" s="20" t="inlineStr">
         <is>
           <t>H | 327呎 (1房)
 $878万
@@ -27588,21 +27626,21 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B21" s="16" t="inlineStr">
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B20" s="20" t="inlineStr">
         <is>
           <t>A | 713呎 (3房)
-$1,951万
+$1951万
 $27,363/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C21" s="16" t="inlineStr">
+      <c r="C20" s="20" t="inlineStr">
         <is>
           <t>B | 326呎 (1房)
 $913万
@@ -27610,39 +27648,39 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D21" s="16" t="inlineStr">
+      <c r="D20" s="20" t="inlineStr">
         <is>
           <t>C | 617呎 (3房)
-$1,729万
+$1729万
 $28,028/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E21" s="16" t="inlineStr">
+      <c r="E20" s="20" t="inlineStr">
         <is>
           <t>D | 443呎 (2房)
-$1,094万
+$1094万
 $24,693/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F21" s="16" t="inlineStr">
+      <c r="F20" s="20" t="inlineStr">
         <is>
           <t>E | 438呎 (2房)
-$1,082万
+$1082万
 $24,712/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G21" s="16" t="inlineStr">
+      <c r="G20" s="20" t="inlineStr">
         <is>
           <t>F | 440呎 (2房)
-$1,118万
+$1118万
 $25,416/呎
 (已售)</t>
         </is>
       </c>
-      <c r="H21" s="16" t="inlineStr">
+      <c r="H20" s="20" t="inlineStr">
         <is>
           <t>G | 326呎 (1房)
 $839万
@@ -27650,7 +27688,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I21" s="16" t="inlineStr">
+      <c r="I20" s="20" t="inlineStr">
         <is>
           <t>H | 327呎 (1房)
 $868万
@@ -27659,21 +27697,21 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B22" s="16" t="inlineStr">
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B21" s="20" t="inlineStr">
         <is>
           <t>A | 714呎 (3房)
-$1,998万
+$1998万
 $27,983/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C22" s="16" t="inlineStr">
+      <c r="C21" s="20" t="inlineStr">
         <is>
           <t>B | 326呎 (1房)
 $936万
@@ -27681,39 +27719,39 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D22" s="16" t="inlineStr">
+      <c r="D21" s="20" t="inlineStr">
         <is>
           <t>C | 616呎 (3房)
-$1,676万
+$1676万
 $27,216/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E22" s="16" t="inlineStr">
+      <c r="E21" s="20" t="inlineStr">
         <is>
           <t>D | 443呎 (2房)
-$1,122万
+$1122万
 $25,327/呎
 (22年-05月)</t>
         </is>
       </c>
-      <c r="F22" s="16" t="inlineStr">
+      <c r="F21" s="20" t="inlineStr">
         <is>
           <t>E | 438呎 (2房)
-$1,110万
+$1110万
 $25,340/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G22" s="16" t="inlineStr">
+      <c r="G21" s="20" t="inlineStr">
         <is>
           <t>F | 440呎 (2房)
-$1,084万
+$1084万
 $24,639/呎
 (已售)</t>
         </is>
       </c>
-      <c r="H22" s="16" t="inlineStr">
+      <c r="H21" s="20" t="inlineStr">
         <is>
           <t>G | 326呎 (1房)
 $837万
@@ -27721,7 +27759,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I22" s="16" t="inlineStr">
+      <c r="I21" s="20" t="inlineStr">
         <is>
           <t>H | 327呎 (1房)
 $866万
@@ -27730,21 +27768,21 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B23" s="16" t="inlineStr">
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B22" s="20" t="inlineStr">
         <is>
           <t>A | 714呎 (3房)
-$1,997万
+$1997万
 $27,975/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C23" s="16" t="inlineStr">
+      <c r="C22" s="20" t="inlineStr">
         <is>
           <t>B | 326呎 (1房)
 $934万
@@ -27752,39 +27790,39 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D23" s="16" t="inlineStr">
+      <c r="D22" s="20" t="inlineStr">
         <is>
           <t>C | 616呎 (3房)
-$1,672万
+$1672万
 $27,135/呎
 (22年-04月)</t>
         </is>
       </c>
-      <c r="E23" s="16" t="inlineStr">
+      <c r="E22" s="20" t="inlineStr">
         <is>
           <t>D | 443呎 (2房)
-$1,090万
+$1090万
 $24,594/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F23" s="16" t="inlineStr">
+      <c r="F22" s="20" t="inlineStr">
         <is>
           <t>E | 438呎 (2房)
-$1,107万
+$1107万
 $25,265/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G23" s="16" t="inlineStr">
+      <c r="G22" s="20" t="inlineStr">
         <is>
           <t>F | 440呎 (2房)
-$1,112万
+$1112万
 $25,266/呎
 (已售)</t>
         </is>
       </c>
-      <c r="H23" s="16" t="inlineStr">
+      <c r="H22" s="20" t="inlineStr">
         <is>
           <t>G | 326呎 (1房)
 $864万
@@ -27792,7 +27830,7 @@
 (26年-05月)</t>
         </is>
       </c>
-      <c r="I23" s="16" t="inlineStr">
+      <c r="I22" s="20" t="inlineStr">
         <is>
           <t>H | 328呎 (1房)
 $864万
@@ -27801,21 +27839,21 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B24" s="16" t="inlineStr">
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B23" s="20" t="inlineStr">
         <is>
           <t>A | 714呎 (3房)
-$1,986万
+$1986万
 $27,822/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C24" s="16" t="inlineStr">
+      <c r="C23" s="20" t="inlineStr">
         <is>
           <t>B | 326呎 (1房)
 $931万
@@ -27823,39 +27861,39 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D24" s="16" t="inlineStr">
+      <c r="D23" s="20" t="inlineStr">
         <is>
           <t>C | 617呎 (3房)
-$1,666万
+$1666万
 $27,010/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E24" s="16" t="inlineStr">
+      <c r="E23" s="20" t="inlineStr">
         <is>
           <t>D | 443呎 (2房)
-$1,088万
+$1088万
 $24,555/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F24" s="16" t="inlineStr">
+      <c r="F23" s="20" t="inlineStr">
         <is>
           <t>E | 438呎 (2房)
-$1,103万
+$1103万
 $25,187/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G24" s="16" t="inlineStr">
+      <c r="G23" s="20" t="inlineStr">
         <is>
           <t>F | 440呎 (2房)
-$1,078万
+$1078万
 $24,493/呎
 (已售)</t>
         </is>
       </c>
-      <c r="H24" s="16" t="inlineStr">
+      <c r="H23" s="20" t="inlineStr">
         <is>
           <t>G | 326呎 (1房)
 $858万
@@ -27863,7 +27901,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I24" s="16" t="inlineStr">
+      <c r="I23" s="20" t="inlineStr">
         <is>
           <t>H | 327呎 (1房)
 $868万
@@ -27872,21 +27910,21 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B25" s="16" t="inlineStr">
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B24" s="20" t="inlineStr">
         <is>
           <t>A | 713呎 (3房)
-$1,920万
+$1920万
 $26,930/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C25" s="16" t="inlineStr">
+      <c r="C24" s="20" t="inlineStr">
         <is>
           <t>B | 326呎 (1房)
 $925万
@@ -27894,39 +27932,39 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D25" s="16" t="inlineStr">
+      <c r="D24" s="20" t="inlineStr">
         <is>
           <t>C | 616呎 (3房)
-$1,704万
+$1704万
 $27,656/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E25" s="16" t="inlineStr">
+      <c r="E24" s="20" t="inlineStr">
         <is>
           <t>D | 443呎 (2房)
-$1,113万
+$1113万
 $25,117/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F25" s="16" t="inlineStr">
+      <c r="F24" s="20" t="inlineStr">
         <is>
           <t>E | 438呎 (2房)
-$1,097万
+$1097万
 $25,039/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G25" s="16" t="inlineStr">
+      <c r="G24" s="20" t="inlineStr">
         <is>
           <t>F | 440呎 (2房)
-$1,102万
+$1102万
 $25,039/呎
 (22年-04月)</t>
         </is>
       </c>
-      <c r="H25" s="16" t="inlineStr">
+      <c r="H24" s="20" t="inlineStr">
         <is>
           <t>G | 326呎 (1房)
 $854万
@@ -27934,7 +27972,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I25" s="16" t="inlineStr">
+      <c r="I24" s="20" t="inlineStr">
         <is>
           <t>H | 327呎 (1房)
 $847万
@@ -27943,21 +27981,21 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B26" s="16" t="inlineStr">
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B25" s="20" t="inlineStr">
         <is>
           <t>A | 713呎 (3房)
-$1,895万
+$1895万
 $26,583/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C26" s="16" t="inlineStr">
+      <c r="C25" s="20" t="inlineStr">
         <is>
           <t>B | 326呎 (1房)
 $920万
@@ -27965,39 +28003,39 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D26" s="16" t="inlineStr">
+      <c r="D25" s="20" t="inlineStr">
         <is>
           <t>C | 617呎 (3房)
-$1,686万
+$1686万
 $27,327/呎
 (22年-04月)</t>
         </is>
       </c>
-      <c r="E26" s="16" t="inlineStr">
+      <c r="E25" s="20" t="inlineStr">
         <is>
           <t>D | 443呎 (2房)
-$1,108万
+$1108万
 $25,023/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F26" s="16" t="inlineStr">
+      <c r="F25" s="20" t="inlineStr">
         <is>
           <t>E | 438呎 (2房)
-$1,092万
+$1092万
 $24,934/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G26" s="16" t="inlineStr">
+      <c r="G25" s="20" t="inlineStr">
         <is>
           <t>F | 440呎 (2房)
-$1,067万
+$1067万
 $24,245/呎
 (已售)</t>
         </is>
       </c>
-      <c r="H26" s="16" t="inlineStr">
+      <c r="H25" s="20" t="inlineStr">
         <is>
           <t>G | 326呎 (1房)
 $852万
@@ -28005,7 +28043,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I26" s="16" t="inlineStr">
+      <c r="I25" s="20" t="inlineStr">
         <is>
           <t>H | 328呎 (1房)
 $857万
@@ -28014,21 +28052,21 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="65" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B27" s="16" t="inlineStr">
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B26" s="20" t="inlineStr">
         <is>
           <t>A | 714呎 (3房)
-$1,890万
+$1890万
 $26,468/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C27" s="16" t="inlineStr">
+      <c r="C26" s="20" t="inlineStr">
         <is>
           <t>B | 326呎 (1房)
 $920万
@@ -28036,39 +28074,39 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D27" s="16" t="inlineStr">
+      <c r="D26" s="20" t="inlineStr">
         <is>
           <t>C | 616呎 (3房)
-$1,643万
+$1643万
 $26,667/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E27" s="16" t="inlineStr">
+      <c r="E26" s="20" t="inlineStr">
         <is>
           <t>D | 443呎 (2房)
-$1,106万
+$1106万
 $24,962/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F27" s="16" t="inlineStr">
+      <c r="F26" s="20" t="inlineStr">
         <is>
           <t>E | 438呎 (2房)
-$1,088万
+$1088万
 $24,829/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G27" s="16" t="inlineStr">
+      <c r="G26" s="20" t="inlineStr">
         <is>
           <t>F | 440呎 (2房)
-$1,092万
+$1092万
 $24,830/呎
 (已售)</t>
         </is>
       </c>
-      <c r="H27" s="16" t="inlineStr">
+      <c r="H26" s="20" t="inlineStr">
         <is>
           <t>G | 326呎 (1房)
 $828万
@@ -28076,7 +28114,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I27" s="16" t="inlineStr">
+      <c r="I26" s="20" t="inlineStr">
         <is>
           <t>H | 328呎 (1房)
 $857万
@@ -28085,21 +28123,21 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="65" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B28" s="16" t="inlineStr">
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B27" s="20" t="inlineStr">
         <is>
           <t>A | 713呎 (3房)
-$1,903万
+$1903万
 $26,690/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C28" s="16" t="inlineStr">
+      <c r="C27" s="20" t="inlineStr">
         <is>
           <t>B | 326呎 (1房)
 $917万
@@ -28107,39 +28145,39 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D28" s="16" t="inlineStr">
+      <c r="D27" s="20" t="inlineStr">
         <is>
           <t>C | 616呎 (3房)
-$1,688万
+$1688万
 $27,409/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E28" s="16" t="inlineStr">
+      <c r="E27" s="20" t="inlineStr">
         <is>
           <t>D | 443呎 (2房)
-$1,072万
+$1072万
 $24,199/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F28" s="16" t="inlineStr">
+      <c r="F27" s="20" t="inlineStr">
         <is>
           <t>E | 438呎 (2房)
-$1,084万
+$1084万
 $24,753/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G28" s="16" t="inlineStr">
+      <c r="G27" s="20" t="inlineStr">
         <is>
           <t>F | 440呎 (2房)
-$1,089万
+$1089万
 $24,755/呎
 (已售)</t>
         </is>
       </c>
-      <c r="H28" s="16" t="inlineStr">
+      <c r="H27" s="20" t="inlineStr">
         <is>
           <t>G | 326呎 (1房)
 $852万
@@ -28147,7 +28185,7 @@
 (25年-06月)</t>
         </is>
       </c>
-      <c r="I28" s="16" t="inlineStr">
+      <c r="I27" s="20" t="inlineStr">
         <is>
           <t>H | 327呎 (1房)
 $857万
@@ -28156,21 +28194,21 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="65" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B29" s="16" t="inlineStr">
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B28" s="20" t="inlineStr">
         <is>
           <t>A | 713呎 (3房)
-$1,845万
+$1845万
 $25,882/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C29" s="16" t="inlineStr">
+      <c r="C28" s="20" t="inlineStr">
         <is>
           <t>B | 326呎 (1房)
 $898万
@@ -28178,39 +28216,39 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D29" s="16" t="inlineStr">
+      <c r="D28" s="20" t="inlineStr">
         <is>
           <t>C | 616呎 (3房)
-$1,597万
+$1597万
 $25,925/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E29" s="16" t="inlineStr">
+      <c r="E28" s="20" t="inlineStr">
         <is>
           <t>D | 443呎 (2房)
-$1,099万
+$1099万
 $24,813/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F29" s="16" t="inlineStr">
+      <c r="F28" s="20" t="inlineStr">
         <is>
           <t>E | 438呎 (2房)
-$1,051万
+$1051万
 $24,000/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G29" s="16" t="inlineStr">
+      <c r="G28" s="20" t="inlineStr">
         <is>
           <t>F | 440呎 (2房)
-$1,086万
+$1086万
 $24,682/呎
 (已售)</t>
         </is>
       </c>
-      <c r="H29" s="16" t="inlineStr">
+      <c r="H28" s="20" t="inlineStr">
         <is>
           <t>G | 326呎 (1房)
 $828万
@@ -28218,7 +28256,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I29" s="16" t="inlineStr">
+      <c r="I28" s="20" t="inlineStr">
         <is>
           <t>H | 327呎 (1房)
 $842万
@@ -28227,21 +28265,21 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="65" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B30" s="16" t="inlineStr">
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B29" s="20" t="inlineStr">
         <is>
           <t>A | 713呎 (3房)
-$1,857万
+$1857万
 $26,045/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C30" s="16" t="inlineStr">
+      <c r="C29" s="20" t="inlineStr">
         <is>
           <t>B | 326呎 (1房)
 $852万
@@ -28249,39 +28287,39 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D30" s="16" t="inlineStr">
+      <c r="D29" s="20" t="inlineStr">
         <is>
           <t>C | 616呎 (3房)
-$1,605万
+$1605万
 $26,062/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E30" s="16" t="inlineStr">
+      <c r="E29" s="20" t="inlineStr">
         <is>
           <t>D | 443呎 (2房)
-$1,067万
+$1067万
 $24,077/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F30" s="16" t="inlineStr">
+      <c r="F29" s="20" t="inlineStr">
         <is>
           <t>E | 438呎 (2房)
-$1,078万
+$1078万
 $24,607/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G30" s="16" t="inlineStr">
+      <c r="G29" s="20" t="inlineStr">
         <is>
           <t>F | 440呎 (2房)
-$1,083万
+$1083万
 $24,607/呎
 (26年-06月)</t>
         </is>
       </c>
-      <c r="H30" s="16" t="inlineStr">
+      <c r="H29" s="20" t="inlineStr">
         <is>
           <t>G | 326呎 (1房)
 $851万
@@ -28289,7 +28327,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I30" s="16" t="inlineStr">
+      <c r="I29" s="20" t="inlineStr">
         <is>
           <t>H | 327呎 (1房)
 $842万
@@ -28298,21 +28336,21 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="65" customHeight="1">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B31" s="16" t="inlineStr">
+    <row r="30" ht="58" customHeight="1">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B30" s="20" t="inlineStr">
         <is>
           <t>A | 713呎 (3房)
-$1,835万
+$1835万
 $25,736/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C31" s="16" t="inlineStr">
+      <c r="C30" s="20" t="inlineStr">
         <is>
           <t>B | 326呎 (1房)
 $865万
@@ -28320,39 +28358,39 @@
 (22年-04月)</t>
         </is>
       </c>
-      <c r="D31" s="16" t="inlineStr">
+      <c r="D30" s="20" t="inlineStr">
         <is>
           <t>C | 616呎 (3房)
-$1,540万
+$1540万
 $25,005/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E31" s="16" t="inlineStr">
+      <c r="E30" s="20" t="inlineStr">
         <is>
           <t>D | 443呎 (2房)
-$1,063万
+$1063万
 $24,005/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F31" s="16" t="inlineStr">
+      <c r="F30" s="20" t="inlineStr">
         <is>
           <t>E | 438呎 (2房)
-$1,075万
+$1075万
 $24,534/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G31" s="16" t="inlineStr">
+      <c r="G30" s="20" t="inlineStr">
         <is>
           <t>F | 440呎 (2房)
-$1,080万
+$1080万
 $24,534/呎
 (已售)</t>
         </is>
       </c>
-      <c r="H31" s="16" t="inlineStr">
+      <c r="H30" s="20" t="inlineStr">
         <is>
           <t>G | 326呎 (1房)
 $851万
@@ -28360,7 +28398,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I31" s="16" t="inlineStr">
+      <c r="I30" s="20" t="inlineStr">
         <is>
           <t>H | 327呎 (1房)
 $856万
@@ -28369,21 +28407,21 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="65" customHeight="1">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B32" s="16" t="inlineStr">
+    <row r="31" ht="58" customHeight="1">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B31" s="20" t="inlineStr">
         <is>
           <t>A | 714呎 (3房)
-$1,809万
+$1809万
 $25,333/呎
 (26年-04月)</t>
         </is>
       </c>
-      <c r="C32" s="16" t="inlineStr">
+      <c r="C31" s="20" t="inlineStr">
         <is>
           <t>B | 326呎 (1房)
 $856万
@@ -28391,39 +28429,39 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D32" s="16" t="inlineStr">
+      <c r="D31" s="20" t="inlineStr">
         <is>
           <t>C | 616呎 (3房)
-$1,564万
+$1564万
 $25,398/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E32" s="16" t="inlineStr">
+      <c r="E31" s="20" t="inlineStr">
         <is>
           <t>D | 443呎 (2房)
-$1,090万
+$1090万
 $24,614/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F32" s="16" t="inlineStr">
+      <c r="F31" s="20" t="inlineStr">
         <is>
           <t>E | 438呎 (2房)
-$1,042万
+$1042万
 $23,785/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G32" s="16" t="inlineStr">
+      <c r="G31" s="20" t="inlineStr">
         <is>
           <t>F | 440呎 (2房)
-$1,046万
+$1046万
 $23,784/呎
 (已售)</t>
         </is>
       </c>
-      <c r="H32" s="16" t="inlineStr">
+      <c r="H31" s="20" t="inlineStr">
         <is>
           <t>G | 326呎 (1房)
 $826万
@@ -28431,7 +28469,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I32" s="16" t="inlineStr">
+      <c r="I31" s="20" t="inlineStr">
         <is>
           <t>H | 327呎 (1房)
 $832万
@@ -28440,21 +28478,21 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="65" customHeight="1">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B33" s="16" t="inlineStr">
+    <row r="32" ht="58" customHeight="1">
+      <c r="A32" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B32" s="20" t="inlineStr">
         <is>
           <t>A | 714呎 (3房)
-$1,808万
+$1808万
 $25,319/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C33" s="16" t="inlineStr">
+      <c r="C32" s="20" t="inlineStr">
         <is>
           <t>B | 326呎 (1房)
 $822万
@@ -28462,39 +28500,39 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D33" s="16" t="inlineStr">
+      <c r="D32" s="20" t="inlineStr">
         <is>
           <t>C | 616呎 (3房)
-$1,519万
+$1519万
 $24,656/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E33" s="16" t="inlineStr">
+      <c r="E32" s="20" t="inlineStr">
         <is>
           <t>D | 443呎 (2房)
-$1,054万
+$1054万
 $23,790/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F33" s="16" t="inlineStr">
+      <c r="F32" s="20" t="inlineStr">
         <is>
           <t>E | 438呎 (2房)
-$1,036万
+$1036万
 $23,642/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G33" s="16" t="inlineStr">
+      <c r="G32" s="20" t="inlineStr">
         <is>
           <t>F | 440呎 (2房)
-$1,070万
+$1070万
 $24,316/呎
 (已售)</t>
         </is>
       </c>
-      <c r="H33" s="16" t="inlineStr">
+      <c r="H32" s="20" t="inlineStr">
         <is>
           <t>G | 326呎 (1房)
 $848万
@@ -28502,7 +28540,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I33" s="16" t="inlineStr">
+      <c r="I32" s="20" t="inlineStr">
         <is>
           <t>H | 327呎 (1房)
 $858万
@@ -28511,21 +28549,21 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="65" customHeight="1">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B34" s="16" t="inlineStr">
+    <row r="33" ht="58" customHeight="1">
+      <c r="A33" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B33" s="20" t="inlineStr">
         <is>
           <t>A | 713呎 (3房)
-$1,695万
+$1695万
 $23,776/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C34" s="16" t="inlineStr">
+      <c r="C33" s="20" t="inlineStr">
         <is>
           <t>B | 326呎 (1房)
 $801万
@@ -28533,39 +28571,39 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D34" s="16" t="inlineStr">
+      <c r="D33" s="20" t="inlineStr">
         <is>
           <t>C | 616呎 (3房)
-$1,468万
+$1468万
 $23,831/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E34" s="16" t="inlineStr">
+      <c r="E33" s="20" t="inlineStr">
         <is>
           <t>D | 443呎 (2房)
-$1,081万
+$1081万
 $24,393/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F34" s="16" t="inlineStr">
+      <c r="F33" s="20" t="inlineStr">
         <is>
           <t>E | 438呎 (2房)
-$1,062万
+$1062万
 $24,242/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G34" s="16" t="inlineStr">
+      <c r="G33" s="20" t="inlineStr">
         <is>
           <t>F | 440呎 (2房)
-$1,067万
+$1067万
 $24,243/呎
 (已售)</t>
         </is>
       </c>
-      <c r="H34" s="16" t="inlineStr">
+      <c r="H33" s="20" t="inlineStr">
         <is>
           <t>G | 326呎 (1房)
 $834万
@@ -28573,7 +28611,7 @@
 (26年-01月)</t>
         </is>
       </c>
-      <c r="I34" s="16" t="inlineStr">
+      <c r="I33" s="20" t="inlineStr">
         <is>
           <t>H | 327呎 (1房)
 $839万
@@ -28582,21 +28620,21 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="65" customHeight="1">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B35" s="16" t="inlineStr">
+    <row r="34" ht="58" customHeight="1">
+      <c r="A34" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B34" s="20" t="inlineStr">
         <is>
           <t>A | 713呎 (3房)
-$1,738万
+$1738万
 $24,377/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C35" s="16" t="inlineStr">
+      <c r="C34" s="20" t="inlineStr">
         <is>
           <t>B | 326呎 (1房)
 $799万
@@ -28604,32 +28642,32 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D35" s="16" t="inlineStr">
+      <c r="D34" s="20" t="inlineStr">
         <is>
           <t>C | 623呎 (3房)
-$1,518万
+$1518万
 $24,374/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E35" s="17" t="inlineStr"/>
-      <c r="F35" s="16" t="inlineStr">
+      <c r="E34" s="21" t="inlineStr"/>
+      <c r="F34" s="20" t="inlineStr">
         <is>
           <t>E | 448呎 (2房)
-$1,082万
+$1082万
 $24,156/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G35" s="16" t="inlineStr">
+      <c r="G34" s="20" t="inlineStr">
         <is>
           <t>F | 440呎 (2房)
-$1,046万
+$1046万
 $23,768/呎
 (24年-01月)</t>
         </is>
       </c>
-      <c r="H35" s="16" t="inlineStr">
+      <c r="H34" s="20" t="inlineStr">
         <is>
           <t>G | 326呎 (1房)
 $852万
@@ -28637,7 +28675,7 @@
 (26年-05月)</t>
         </is>
       </c>
-      <c r="I35" s="18" t="inlineStr">
+      <c r="I34" s="22" t="inlineStr">
         <is>
           <t>H | 328呎 (1房)
 $942万
@@ -28646,21 +28684,21 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="65" customHeight="1">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B36" s="16" t="inlineStr">
+    <row r="35" ht="58" customHeight="1">
+      <c r="A35" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B35" s="20" t="inlineStr">
         <is>
           <t>A | 713呎 (3房)
-$1,704万
+$1704万
 $23,902/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C36" s="16" t="inlineStr">
+      <c r="C35" s="20" t="inlineStr">
         <is>
           <t>B | 326呎 (1房)
 $819万
@@ -28668,23 +28706,23 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D36" s="16" t="inlineStr">
+      <c r="D35" s="20" t="inlineStr">
         <is>
           <t>C | 623呎 (3房)
-$1,514万
+$1514万
 $24,302/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E36" s="17" t="inlineStr"/>
-      <c r="F36" s="17" t="inlineStr"/>
-      <c r="G36" s="17" t="inlineStr"/>
-      <c r="H36" s="17" t="inlineStr"/>
-      <c r="I36" s="17" t="inlineStr"/>
+      <c r="E35" s="21" t="inlineStr"/>
+      <c r="F35" s="21" t="inlineStr"/>
+      <c r="G35" s="21" t="inlineStr"/>
+      <c r="H35" s="21" t="inlineStr"/>
+      <c r="I35" s="21" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -28697,2048 +28735,2048 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H36"/>
+  <dimension ref="A1:H35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Monaco Marine - 1B座 销控网格图</t>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>1B座 销控网格图</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>总套数</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="8" t="inlineStr">
         <is>
           <t>在售 (Sale)</t>
         </is>
       </c>
-      <c r="C2" s="8" t="inlineStr">
+      <c r="C2" s="9" t="inlineStr">
         <is>
           <t>已定价未售</t>
         </is>
       </c>
-      <c r="D2" s="9" t="inlineStr">
+      <c r="D2" s="10" t="inlineStr">
         <is>
           <t>已售 (Sold)</t>
         </is>
       </c>
-      <c r="E2" s="10" t="inlineStr">
+      <c r="E2" s="11" t="inlineStr">
         <is>
           <t>暂停销售</t>
         </is>
       </c>
-      <c r="F2" s="6" t="inlineStr">
+      <c r="F2" s="12" t="inlineStr">
         <is>
           <t>待售 (Pending)</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>213 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>213 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>213</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>213</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C4" s="19" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D4" s="19" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E4" s="19" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F4" s="19" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G4" s="19" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H4" s="19" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>38/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
         <is>
           <t>A | 1570呎 (4+房)
-$6,680万
+$6680万
 $42,548/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C6" s="17" t="inlineStr"/>
-      <c r="D6" s="17" t="inlineStr"/>
-      <c r="E6" s="17" t="inlineStr"/>
-      <c r="F6" s="16" t="inlineStr">
+      <c r="C5" s="21" t="inlineStr"/>
+      <c r="D5" s="21" t="inlineStr"/>
+      <c r="E5" s="21" t="inlineStr"/>
+      <c r="F5" s="20" t="inlineStr">
         <is>
           <t>E | 447呎 (2房)
-$1,176万
+$1176万
 $26,298/呎
 (26年-03月)</t>
         </is>
       </c>
-      <c r="G6" s="16" t="inlineStr">
+      <c r="G5" s="20" t="inlineStr">
         <is>
           <t>F | 435呎 (2房)
-$1,130万
+$1130万
 $25,966/呎
 (26年-03月)</t>
         </is>
       </c>
-      <c r="H6" s="16" t="inlineStr">
+      <c r="H5" s="20" t="inlineStr">
         <is>
           <t>G | 455呎 (2房)
-$1,190万
+$1190万
 $26,158/呎
 (26年-03月)</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>37/F</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
         <is>
           <t>A | 525呎 (2房)
-$1,556万
+$1556万
 $29,642/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C7" s="16" t="inlineStr">
+      <c r="C6" s="20" t="inlineStr">
         <is>
           <t>B | 574呎 (3房)
-$1,650万
+$1650万
 $28,754/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D7" s="16" t="inlineStr">
+      <c r="D6" s="20" t="inlineStr">
         <is>
           <t>C | 457呎 (2房)
-$1,323万
+$1323万
 $28,958/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E7" s="16" t="inlineStr">
+      <c r="E6" s="20" t="inlineStr">
         <is>
           <t>D | 435呎 (2房)
-$1,260万
+$1260万
 $28,975/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F7" s="16" t="inlineStr">
+      <c r="F6" s="20" t="inlineStr">
         <is>
           <t>E | 449呎 (2房)
-$1,176万
+$1176万
 $26,198/呎
 (24年-05月)</t>
         </is>
       </c>
-      <c r="G7" s="16" t="inlineStr">
+      <c r="G6" s="20" t="inlineStr">
         <is>
           <t>F | 435呎 (2房)
-$1,123万
+$1123万
 $25,809/呎
 (26年-02月)</t>
         </is>
       </c>
-      <c r="H7" s="16" t="inlineStr">
+      <c r="H6" s="20" t="inlineStr">
         <is>
           <t>G | 455呎 (2房)
-$1,185万
+$1185万
 $26,051/呎
 (26年-02月)</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>36/F</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="inlineStr">
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
         <is>
           <t>A | 525呎 (2房)
-$1,513万
+$1513万
 $28,819/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C8" s="16" t="inlineStr">
+      <c r="C7" s="20" t="inlineStr">
         <is>
           <t>B | 574呎 (3房)
-$1,664万
+$1664万
 $28,995/呎
 (24年-03月)</t>
         </is>
       </c>
-      <c r="D8" s="16" t="inlineStr">
+      <c r="D7" s="20" t="inlineStr">
         <is>
           <t>C | 457呎 (2房)
-$1,283万
+$1283万
 $28,074/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E8" s="16" t="inlineStr">
+      <c r="E7" s="20" t="inlineStr">
         <is>
           <t>D | 435呎 (2房)
-$1,225万
+$1225万
 $28,161/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F8" s="16" t="inlineStr">
+      <c r="F7" s="20" t="inlineStr">
         <is>
           <t>E | 450呎 (2房)
-$1,174万
+$1174万
 $26,093/呎
 (25年-12月)</t>
         </is>
       </c>
-      <c r="G8" s="16" t="inlineStr">
+      <c r="G7" s="20" t="inlineStr">
         <is>
           <t>F | 435呎 (2房)
-$1,119万
+$1119万
 $25,733/呎
 (24年-08月)</t>
         </is>
       </c>
-      <c r="H8" s="16" t="inlineStr">
+      <c r="H7" s="20" t="inlineStr">
         <is>
           <t>G | 462呎 (2房)
-$1,186万
+$1186万
 $25,682/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>35/F</t>
-        </is>
-      </c>
-      <c r="B9" s="16" t="inlineStr">
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
         <is>
           <t>A | 525呎 (2房)
-$1,513万
+$1513万
 $28,817/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C9" s="16" t="inlineStr">
+      <c r="C8" s="20" t="inlineStr">
         <is>
           <t>B | 574呎 (3房)
-$1,659万
+$1659万
 $28,908/呎
 (24年-03月)</t>
         </is>
       </c>
-      <c r="D9" s="16" t="inlineStr">
+      <c r="D8" s="20" t="inlineStr">
         <is>
           <t>C | 457呎 (2房)
-$1,279万
+$1279万
 $27,991/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E9" s="16" t="inlineStr">
+      <c r="E8" s="20" t="inlineStr">
         <is>
           <t>D | 435呎 (2房)
-$1,229万
+$1229万
 $28,251/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F9" s="16" t="inlineStr">
+      <c r="F8" s="20" t="inlineStr">
         <is>
           <t>E | 450呎 (2房)
-$1,212万
+$1212万
 $26,942/呎
 (26年-03月)</t>
         </is>
       </c>
-      <c r="G9" s="16" t="inlineStr">
+      <c r="G8" s="20" t="inlineStr">
         <is>
           <t>F | 435呎 (2房)
-$1,116万
+$1116万
 $25,655/呎
 (26年-03月)</t>
         </is>
       </c>
-      <c r="H9" s="16" t="inlineStr">
+      <c r="H8" s="20" t="inlineStr">
         <is>
           <t>G | 462呎 (2房)
-$1,196万
+$1196万
 $25,894/呎
 (26年-02月)</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>33/F</t>
-        </is>
-      </c>
-      <c r="B10" s="16" t="inlineStr">
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
         <is>
           <t>A | 525呎 (2房)
-$1,510万
+$1510万
 $28,760/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C10" s="16" t="inlineStr">
+      <c r="C9" s="20" t="inlineStr">
         <is>
           <t>B | 574呎 (3房)
-$1,654万
+$1654万
 $28,821/呎
 (24年-04月)</t>
         </is>
       </c>
-      <c r="D10" s="16" t="inlineStr">
+      <c r="D9" s="20" t="inlineStr">
         <is>
           <t>C | 457呎 (2房)
-$1,312万
+$1312万
 $28,700/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E10" s="16" t="inlineStr">
+      <c r="E9" s="20" t="inlineStr">
         <is>
           <t>D | 435呎 (2房)
-$1,254万
+$1254万
 $28,830/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F10" s="16" t="inlineStr">
+      <c r="F9" s="20" t="inlineStr">
         <is>
           <t>E | 450呎 (2房)
-$1,167万
+$1167万
 $25,938/呎
 (26年-03月)</t>
         </is>
       </c>
-      <c r="G10" s="16" t="inlineStr">
+      <c r="G9" s="20" t="inlineStr">
         <is>
           <t>F | 435呎 (2房)
-$1,113万
+$1113万
 $25,579/呎
 (25年-08月)</t>
         </is>
       </c>
-      <c r="H10" s="16" t="inlineStr">
+      <c r="H9" s="20" t="inlineStr">
         <is>
           <t>G | 462呎 (2房)
-$1,193万
+$1193万
 $25,816/呎
 (26年-01月)</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>32/F</t>
-        </is>
-      </c>
-      <c r="B11" s="16" t="inlineStr">
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
         <is>
           <t>A | 525呎 (2房)
-$1,508万
+$1508万
 $28,730/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C11" s="16" t="inlineStr">
+      <c r="C10" s="20" t="inlineStr">
         <is>
           <t>B | 574呎 (3房)
-$1,631万
+$1631万
 $28,413/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D11" s="16" t="inlineStr">
+      <c r="D10" s="20" t="inlineStr">
         <is>
           <t>C | 457呎 (2房)
-$1,308万
+$1308万
 $28,615/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E11" s="16" t="inlineStr">
+      <c r="E10" s="20" t="inlineStr">
         <is>
           <t>D | 435呎 (2房)
-$1,253万
+$1253万
 $28,800/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F11" s="16" t="inlineStr">
+      <c r="F10" s="20" t="inlineStr">
         <is>
           <t>E | 450呎 (2房)
-$1,164万
+$1164万
 $25,860/呎
 (26年-03月)</t>
         </is>
       </c>
-      <c r="G11" s="16" t="inlineStr">
+      <c r="G10" s="20" t="inlineStr">
         <is>
           <t>F | 435呎 (2房)
-$1,109万
+$1109万
 $25,501/呎
 (24年-09月)</t>
         </is>
       </c>
-      <c r="H11" s="16" t="inlineStr">
+      <c r="H10" s="20" t="inlineStr">
         <is>
           <t>G | 462呎 (2房)
-$1,189万
+$1189万
 $25,740/呎
 (26年-01月)</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>31/F</t>
-        </is>
-      </c>
-      <c r="B12" s="16" t="inlineStr">
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B11" s="20" t="inlineStr">
         <is>
           <t>A | 524呎 (2房)
-$1,505万
+$1505万
 $28,727/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C12" s="16" t="inlineStr">
+      <c r="C11" s="20" t="inlineStr">
         <is>
           <t>B | 574呎 (3房)
-$1,644万
+$1644万
 $28,648/呎
 (23年-09月)</t>
         </is>
       </c>
-      <c r="D12" s="16" t="inlineStr">
+      <c r="D11" s="20" t="inlineStr">
         <is>
           <t>C | 457呎 (2房)
-$1,304万
+$1304万
 $28,530/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E12" s="16" t="inlineStr">
+      <c r="E11" s="20" t="inlineStr">
         <is>
           <t>D | 435呎 (2房)
-$1,222万
+$1222万
 $28,080/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F12" s="16" t="inlineStr">
+      <c r="F11" s="20" t="inlineStr">
         <is>
           <t>E | 450呎 (2房)
-$1,160万
+$1160万
 $25,782/呎
 (25年-11月)</t>
         </is>
       </c>
-      <c r="G12" s="16" t="inlineStr">
+      <c r="G11" s="20" t="inlineStr">
         <is>
           <t>F | 435呎 (2房)
-$1,106万
+$1106万
 $25,428/呎
 (24年-05月)</t>
         </is>
       </c>
-      <c r="H12" s="16" t="inlineStr">
+      <c r="H11" s="20" t="inlineStr">
         <is>
           <t>G | 462呎 (2房)
-$1,206万
+$1206万
 $26,095/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>30/F</t>
-        </is>
-      </c>
-      <c r="B13" s="16" t="inlineStr">
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="inlineStr">
         <is>
           <t>A | 525呎 (2房)
-$1,502万
+$1502万
 $28,613/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C13" s="16" t="inlineStr">
+      <c r="C12" s="20" t="inlineStr">
         <is>
           <t>B | 574呎 (3房)
-$1,640万
+$1640万
 $28,563/呎
 (24年-04月)</t>
         </is>
       </c>
-      <c r="D13" s="16" t="inlineStr">
+      <c r="D12" s="20" t="inlineStr">
         <is>
           <t>C | 457呎 (2房)
-$1,300万
+$1300万
 $28,444/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E13" s="16" t="inlineStr">
+      <c r="E12" s="20" t="inlineStr">
         <is>
           <t>D | 435呎 (2房)
-$1,247万
+$1247万
 $28,657/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F13" s="16" t="inlineStr">
+      <c r="F12" s="20" t="inlineStr">
         <is>
           <t>E | 450呎 (2房)
-$1,157万
+$1157万
 $25,704/呎
 (24年-09月)</t>
         </is>
       </c>
-      <c r="G13" s="16" t="inlineStr">
+      <c r="G12" s="20" t="inlineStr">
         <is>
           <t>F | 435呎 (2房)
-$1,103万
+$1103万
 $25,352/呎
 (24年-05月)</t>
         </is>
       </c>
-      <c r="H13" s="16" t="inlineStr">
+      <c r="H12" s="20" t="inlineStr">
         <is>
           <t>G | 462呎 (2房)
-$1,202万
+$1202万
 $26,017/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>29/F</t>
-        </is>
-      </c>
-      <c r="B14" s="16" t="inlineStr">
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
         <is>
           <t>A | 525呎 (2房)
-$1,542万
+$1542万
 $29,368/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C14" s="16" t="inlineStr">
+      <c r="C13" s="20" t="inlineStr">
         <is>
           <t>B | 574呎 (3房)
-$1,635万
+$1635万
 $28,477/呎
 (24年-04月)</t>
         </is>
       </c>
-      <c r="D14" s="16" t="inlineStr">
+      <c r="D13" s="20" t="inlineStr">
         <is>
           <t>C | 457呎 (2房)
-$1,296万
+$1296万
 $28,359/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E14" s="16" t="inlineStr">
+      <c r="E13" s="20" t="inlineStr">
         <is>
           <t>D | 435呎 (2房)
-$1,222万
+$1222万
 $28,099/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F14" s="16" t="inlineStr">
+      <c r="F13" s="20" t="inlineStr">
         <is>
           <t>E | 450呎 (2房)
-$1,153万
+$1153万
 $25,629/呎
 (26年-03月)</t>
         </is>
       </c>
-      <c r="G14" s="16" t="inlineStr">
+      <c r="G13" s="20" t="inlineStr">
         <is>
           <t>F | 435呎 (2房)
-$1,100万
+$1100万
 $25,276/呎
 (24年-05月)</t>
         </is>
       </c>
-      <c r="H14" s="16" t="inlineStr">
+      <c r="H13" s="20" t="inlineStr">
         <is>
           <t>G | 462呎 (2房)
-$1,179万
+$1179万
 $25,511/呎
 (25年-04月)</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>28/F</t>
-        </is>
-      </c>
-      <c r="B15" s="16" t="inlineStr">
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
         <is>
           <t>A | 525呎 (2房)
-$1,539万
+$1539万
 $29,309/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C15" s="16" t="inlineStr">
+      <c r="C14" s="20" t="inlineStr">
         <is>
           <t>B | 574呎 (3房)
-$1,657万
+$1657万
 $28,871/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D15" s="16" t="inlineStr">
+      <c r="D14" s="20" t="inlineStr">
         <is>
           <t>C | 457呎 (2房)
-$1,292万
+$1292万
 $28,274/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E15" s="16" t="inlineStr">
+      <c r="E14" s="20" t="inlineStr">
         <is>
           <t>D | 435呎 (2房)
-$1,219万
+$1219万
 $28,014/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F15" s="16" t="inlineStr">
+      <c r="F14" s="20" t="inlineStr">
         <is>
           <t>E | 450呎 (2房)
-$1,150万
+$1150万
 $25,551/呎
 (24年-04月)</t>
         </is>
       </c>
-      <c r="G15" s="16" t="inlineStr">
+      <c r="G14" s="20" t="inlineStr">
         <is>
           <t>F | 435呎 (2房)
-$1,096万
+$1096万
 $25,200/呎
 (24年-05月)</t>
         </is>
       </c>
-      <c r="H15" s="16" t="inlineStr">
+      <c r="H14" s="20" t="inlineStr">
         <is>
           <t>G | 462呎 (2房)
-$1,162万
+$1162万
 $25,147/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>27/F</t>
-        </is>
-      </c>
-      <c r="B16" s="16" t="inlineStr">
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
         <is>
           <t>A | 525呎 (2房)
-$1,529万
+$1529万
 $29,130/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C16" s="16" t="inlineStr">
+      <c r="C15" s="20" t="inlineStr">
         <is>
           <t>B | 574呎 (3房)
-$1,620万
+$1620万
 $28,223/呎
 (24年-04月)</t>
         </is>
       </c>
-      <c r="D16" s="16" t="inlineStr">
+      <c r="D15" s="20" t="inlineStr">
         <is>
           <t>C | 457呎 (2房)
-$1,284万
+$1284万
 $28,105/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E16" s="16" t="inlineStr">
+      <c r="E15" s="20" t="inlineStr">
         <is>
           <t>D | 435呎 (2房)
-$1,210万
+$1210万
 $27,821/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F16" s="16" t="inlineStr">
+      <c r="F15" s="20" t="inlineStr">
         <is>
           <t>E | 449呎 (2房)
-$1,161万
+$1161万
 $25,855/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G16" s="16" t="inlineStr">
+      <c r="G15" s="20" t="inlineStr">
         <is>
           <t>F | 435呎 (2房)
-$1,088万
+$1088万
 $25,018/呎
 (24年-04月)</t>
         </is>
       </c>
-      <c r="H16" s="16" t="inlineStr">
+      <c r="H15" s="20" t="inlineStr">
         <is>
           <t>G | 462呎 (2房)
-$1,168万
+$1168万
 $25,281/呎
 (24年-05月)</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B17" s="16" t="inlineStr">
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
         <is>
           <t>A | 524呎 (2房)
-$1,483万
+$1483万
 $28,309/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C17" s="16" t="inlineStr">
+      <c r="C16" s="20" t="inlineStr">
         <is>
           <t>B | 574呎 (3房)
-$1,615万
+$1615万
 $28,138/呎
 (23年-07月)</t>
         </is>
       </c>
-      <c r="D17" s="16" t="inlineStr">
+      <c r="D16" s="20" t="inlineStr">
         <is>
           <t>C | 457呎 (2房)
-$1,245万
+$1245万
 $27,247/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E17" s="16" t="inlineStr">
+      <c r="E16" s="20" t="inlineStr">
         <is>
           <t>D | 435呎 (2房)
-$1,227万
+$1227万
 $28,205/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F17" s="16" t="inlineStr">
+      <c r="F16" s="20" t="inlineStr">
         <is>
           <t>E | 450呎 (2房)
-$1,138万
+$1138万
 $25,293/呎
 (24年-04月)</t>
         </is>
       </c>
-      <c r="G17" s="16" t="inlineStr">
+      <c r="G16" s="20" t="inlineStr">
         <is>
           <t>F | 435呎 (2房)
-$1,085万
+$1085万
 $24,943/呎
 (24年-04月)</t>
         </is>
       </c>
-      <c r="H17" s="16" t="inlineStr">
+      <c r="H16" s="20" t="inlineStr">
         <is>
           <t>G | 462呎 (2房)
-$1,164万
+$1164万
 $25,206/呎
 (25年-02月)</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B18" s="16" t="inlineStr">
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B17" s="20" t="inlineStr">
         <is>
           <t>A | 524呎 (2房)
-$1,514万
+$1514万
 $28,903/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C18" s="16" t="inlineStr">
+      <c r="C17" s="20" t="inlineStr">
         <is>
           <t>B | 574呎 (3房)
-$1,669万
+$1669万
 $29,078/呎
 (24年-04月)</t>
         </is>
       </c>
-      <c r="D18" s="16" t="inlineStr">
+      <c r="D17" s="20" t="inlineStr">
         <is>
           <t>C | 457呎 (2房)
-$1,277万
+$1277万
 $27,937/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E18" s="16" t="inlineStr">
+      <c r="E17" s="20" t="inlineStr">
         <is>
           <t>D | 435呎 (2房)
-$1,203万
+$1203万
 $27,655/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F18" s="16" t="inlineStr">
+      <c r="F17" s="20" t="inlineStr">
         <is>
           <t>E | 449呎 (2房)
-$1,135万
+$1135万
 $25,274/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G18" s="16" t="inlineStr">
+      <c r="G17" s="20" t="inlineStr">
         <is>
           <t>F | 435呎 (2房)
-$1,165万
+$1165万
 $26,777/呎
 (25年-08月)</t>
         </is>
       </c>
-      <c r="H18" s="16" t="inlineStr">
+      <c r="H17" s="20" t="inlineStr">
         <is>
           <t>G | 462呎 (2房)
-$1,161万
+$1161万
 $25,132/呎
 (25年-01月)</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B19" s="16" t="inlineStr">
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B18" s="20" t="inlineStr">
         <is>
           <t>A | 525呎 (2房)
-$1,462万
+$1462万
 $27,848/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C19" s="16" t="inlineStr">
+      <c r="C18" s="20" t="inlineStr">
         <is>
           <t>B | 574呎 (3房)
-$1,633万
+$1633万
 $28,443/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D19" s="16" t="inlineStr">
+      <c r="D18" s="20" t="inlineStr">
         <is>
           <t>C | 457呎 (2房)
-$1,273万
+$1273万
 $27,853/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E19" s="16" t="inlineStr">
+      <c r="E18" s="20" t="inlineStr">
         <is>
           <t>D | 435呎 (2房)
-$1,218万
+$1218万
 $28,009/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F19" s="16" t="inlineStr">
+      <c r="F18" s="20" t="inlineStr">
         <is>
           <t>E | 450呎 (2房)
-$1,131万
+$1131万
 $25,142/呎
 (26年-03月)</t>
         </is>
       </c>
-      <c r="G19" s="16" t="inlineStr">
+      <c r="G18" s="20" t="inlineStr">
         <is>
           <t>F | 435呎 (2房)
-$1,079万
+$1079万
 $24,795/呎
 (24年-01月)</t>
         </is>
       </c>
-      <c r="H19" s="16" t="inlineStr">
+      <c r="H18" s="20" t="inlineStr">
         <is>
           <t>G | 462呎 (2房)
-$1,155万
+$1155万
 $25,009/呎
 (25年-11月)</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B20" s="16" t="inlineStr">
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B19" s="20" t="inlineStr">
         <is>
           <t>A | 524呎 (2房)
-$1,496万
+$1496万
 $28,553/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C20" s="16" t="inlineStr">
+      <c r="C19" s="20" t="inlineStr">
         <is>
           <t>B | 574呎 (3房)
-$1,628万
+$1628万
 $28,357/呎
 (26年-03月)</t>
         </is>
       </c>
-      <c r="D20" s="16" t="inlineStr">
+      <c r="D19" s="20" t="inlineStr">
         <is>
           <t>C | 457呎 (2房)
-$1,269万
+$1269万
 $27,770/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E20" s="16" t="inlineStr">
+      <c r="E19" s="20" t="inlineStr">
         <is>
           <t>D | 435呎 (2房)
-$1,186万
+$1186万
 $27,253/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F20" s="16" t="inlineStr">
+      <c r="F19" s="20" t="inlineStr">
         <is>
           <t>E | 449呎 (2房)
-$1,147万
+$1147万
 $25,546/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G20" s="16" t="inlineStr">
+      <c r="G19" s="20" t="inlineStr">
         <is>
           <t>F | 435呎 (2房)
-$1,075万
+$1075万
 $24,720/呎
 (23年-12月)</t>
         </is>
       </c>
-      <c r="H20" s="16" t="inlineStr">
+      <c r="H19" s="20" t="inlineStr">
         <is>
           <t>G | 462呎 (2房)
-$1,150万
+$1150万
 $24,887/呎
 (24年-09月)</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B21" s="16" t="inlineStr">
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B20" s="20" t="inlineStr">
         <is>
           <t>A | 525呎 (2房)
-$1,444万
+$1444万
 $27,510/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C21" s="16" t="inlineStr">
+      <c r="C20" s="20" t="inlineStr">
         <is>
           <t>B | 574呎 (3房)
-$1,592万
+$1592万
 $27,742/呎
 (24年-01月)</t>
         </is>
       </c>
-      <c r="D21" s="16" t="inlineStr">
+      <c r="D20" s="20" t="inlineStr">
         <is>
           <t>C | 457呎 (2房)
-$1,264万
+$1264万
 $27,661/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E21" s="16" t="inlineStr">
+      <c r="E20" s="20" t="inlineStr">
         <is>
           <t>D | 435呎 (2房)
-$1,171万
+$1171万
 $26,910/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F21" s="16" t="inlineStr">
+      <c r="F20" s="20" t="inlineStr">
         <is>
           <t>E | 450呎 (2房)
-$1,125万
+$1125万
 $24,993/呎
 (26年-02月)</t>
         </is>
       </c>
-      <c r="G21" s="16" t="inlineStr">
+      <c r="G20" s="20" t="inlineStr">
         <is>
           <t>F | 435呎 (2房)
-$1,072万
+$1072万
 $24,646/呎
 (24年-04月)</t>
         </is>
       </c>
-      <c r="H21" s="16" t="inlineStr">
+      <c r="H20" s="20" t="inlineStr">
         <is>
           <t>G | 462呎 (2房)
-$1,129万
+$1129万
 $24,439/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B22" s="16" t="inlineStr">
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B21" s="20" t="inlineStr">
         <is>
           <t>A | 525呎 (2房)
-$1,434万
+$1434万
 $27,310/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C22" s="16" t="inlineStr">
+      <c r="C21" s="20" t="inlineStr">
         <is>
           <t>B | 574呎 (3房)
-$1,616万
+$1616万
 $28,153/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D22" s="16" t="inlineStr">
+      <c r="D21" s="20" t="inlineStr">
         <is>
           <t>C | 457呎 (2房)
-$1,262万
+$1262万
 $27,604/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E22" s="16" t="inlineStr">
+      <c r="E21" s="20" t="inlineStr">
         <is>
           <t>D | 435呎 (2房)
-$1,191万
+$1191万
 $27,379/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F22" s="16" t="inlineStr">
+      <c r="F21" s="20" t="inlineStr">
         <is>
           <t>E | 450呎 (2房)
-$1,121万
+$1121万
 $24,918/呎
 (24年-08月)</t>
         </is>
       </c>
-      <c r="G22" s="16" t="inlineStr">
+      <c r="G21" s="20" t="inlineStr">
         <is>
           <t>F | 435呎 (2房)
-$1,069万
+$1069万
 $24,572/呎
 (24年-04月)</t>
         </is>
       </c>
-      <c r="H22" s="16" t="inlineStr">
+      <c r="H21" s="20" t="inlineStr">
         <is>
           <t>G | 462呎 (2房)
-$1,121万
+$1121万
 $24,271/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B23" s="16" t="inlineStr">
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B22" s="20" t="inlineStr">
         <is>
           <t>A | 524呎 (2房)
-$1,416万
+$1416万
 $27,031/呎
 (24年-07月)</t>
         </is>
       </c>
-      <c r="C23" s="16" t="inlineStr">
+      <c r="C22" s="20" t="inlineStr">
         <is>
           <t>B | 574呎 (3房)
-$1,611万
+$1611万
 $28,070/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D23" s="16" t="inlineStr">
+      <c r="D22" s="20" t="inlineStr">
         <is>
           <t>C | 457呎 (2房)
-$1,258万
+$1258万
 $27,521/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E23" s="16" t="inlineStr">
+      <c r="E22" s="20" t="inlineStr">
         <is>
           <t>D | 435呎 (2房)
-$1,149万
+$1149万
 $26,409/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F23" s="16" t="inlineStr">
+      <c r="F22" s="20" t="inlineStr">
         <is>
           <t>E | 450呎 (2房)
-$1,118万
+$1118万
 $24,842/呎
 (24年-04月)</t>
         </is>
       </c>
-      <c r="G23" s="16" t="inlineStr">
+      <c r="G22" s="20" t="inlineStr">
         <is>
           <t>F | 435呎 (2房)
-$1,066万
+$1066万
 $24,499/呎
 (24年-01月)</t>
         </is>
       </c>
-      <c r="H23" s="16" t="inlineStr">
+      <c r="H22" s="20" t="inlineStr">
         <is>
           <t>G | 462呎 (2房)
-$1,114万
+$1114万
 $24,106/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B24" s="16" t="inlineStr">
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B23" s="20" t="inlineStr">
         <is>
           <t>A | 525呎 (2房)
-$1,446万
+$1446万
 $27,543/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C24" s="16" t="inlineStr">
+      <c r="C23" s="20" t="inlineStr">
         <is>
           <t>B | 574呎 (3房)
-$1,581万
+$1581万
 $27,549/呎
 (24年-01月)</t>
         </is>
       </c>
-      <c r="D24" s="16" t="inlineStr">
+      <c r="D23" s="20" t="inlineStr">
         <is>
           <t>C | 457呎 (2房)
-$1,254万
+$1254万
 $27,440/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E24" s="16" t="inlineStr">
+      <c r="E23" s="20" t="inlineStr">
         <is>
           <t>D | 435呎 (2房)
-$1,172万
+$1172万
 $26,943/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F24" s="16" t="inlineStr">
+      <c r="F23" s="20" t="inlineStr">
         <is>
           <t>E | 450呎 (2房)
-$1,115万
+$1115万
 $24,769/呎
 (25年-12月)</t>
         </is>
       </c>
-      <c r="G24" s="16" t="inlineStr">
+      <c r="G23" s="20" t="inlineStr">
         <is>
           <t>F | 435呎 (2房)
-$1,051万
+$1051万
 $24,152/呎
 (22年-04月)</t>
         </is>
       </c>
-      <c r="H24" s="16" t="inlineStr">
+      <c r="H23" s="20" t="inlineStr">
         <is>
           <t>G | 462呎 (2房)
-$1,112万
+$1112万
 $24,080/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B25" s="16" t="inlineStr">
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B24" s="20" t="inlineStr">
         <is>
           <t>A | 525呎 (2房)
-$1,431万
+$1431万
 $27,257/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C25" s="16" t="inlineStr">
+      <c r="C24" s="20" t="inlineStr">
         <is>
           <t>B | 574呎 (3房)
-$1,555万
+$1555万
 $27,084/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D25" s="16" t="inlineStr">
+      <c r="D24" s="20" t="inlineStr">
         <is>
           <t>C | 457呎 (2房)
-$1,246万
+$1246万
 $27,276/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E25" s="16" t="inlineStr">
+      <c r="E24" s="20" t="inlineStr">
         <is>
           <t>D | 435呎 (2房)
-$1,127万
+$1127万
 $25,910/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F25" s="16" t="inlineStr">
+      <c r="F24" s="20" t="inlineStr">
         <is>
           <t>E | 450呎 (2房)
-$1,108万
+$1108万
 $24,620/呎
 (26年-02月)</t>
         </is>
       </c>
-      <c r="G25" s="16" t="inlineStr">
+      <c r="G24" s="20" t="inlineStr">
         <is>
           <t>F | 435呎 (2房)
-$1,074万
+$1074万
 $24,690/呎
 (已售)</t>
         </is>
       </c>
-      <c r="H25" s="16" t="inlineStr">
+      <c r="H24" s="20" t="inlineStr">
         <is>
           <t>G | 462呎 (2房)
-$1,142万
+$1142万
 $24,712/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B26" s="16" t="inlineStr">
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B25" s="20" t="inlineStr">
         <is>
           <t>A | 525呎 (2房)
-$1,413万
+$1413万
 $26,909/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C26" s="16" t="inlineStr">
+      <c r="C25" s="20" t="inlineStr">
         <is>
           <t>B | 574呎 (3房)
-$1,546万
+$1546万
 $26,934/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D26" s="16" t="inlineStr">
+      <c r="D25" s="20" t="inlineStr">
         <is>
           <t>C | 457呎 (2房)
-$1,207万
+$1207万
 $26,411/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E26" s="16" t="inlineStr">
+      <c r="E25" s="20" t="inlineStr">
         <is>
           <t>D | 435呎 (2房)
-$1,146万
+$1146万
 $26,345/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F26" s="16" t="inlineStr">
+      <c r="F25" s="20" t="inlineStr">
         <is>
           <t>E | 450呎 (2房)
-$1,103万
+$1103万
 $24,518/呎
 (24年-05月)</t>
         </is>
       </c>
-      <c r="G26" s="16" t="inlineStr">
+      <c r="G25" s="20" t="inlineStr">
         <is>
           <t>F | 435呎 (2房)
-$1,040万
+$1040万
 $23,906/呎
 (已售)</t>
         </is>
       </c>
-      <c r="H26" s="16" t="inlineStr">
+      <c r="H25" s="20" t="inlineStr">
         <is>
           <t>G | 462呎 (2房)
-$1,139万
+$1139万
 $24,656/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="65" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B27" s="16" t="inlineStr">
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B26" s="20" t="inlineStr">
         <is>
           <t>A | 525呎 (2房)
-$1,373万
+$1373万
 $26,145/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C27" s="16" t="inlineStr">
+      <c r="C26" s="20" t="inlineStr">
         <is>
           <t>B | 574呎 (3房)
-$1,542万
+$1542万
 $26,855/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D27" s="16" t="inlineStr">
+      <c r="D26" s="20" t="inlineStr">
         <is>
           <t>C | 457呎 (2房)
-$1,238万
+$1238万
 $27,079/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E27" s="16" t="inlineStr">
+      <c r="E26" s="20" t="inlineStr">
         <is>
           <t>D | 435呎 (2房)
-$1,145万
+$1145万
 $26,320/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F27" s="16" t="inlineStr">
+      <c r="F26" s="20" t="inlineStr">
         <is>
           <t>E | 450呎 (2房)
-$1,099万
+$1099万
 $24,416/呎
 (25年-11月)</t>
         </is>
       </c>
-      <c r="G27" s="16" t="inlineStr">
+      <c r="G26" s="20" t="inlineStr">
         <is>
           <t>F | 435呎 (2房)
-$1,065万
+$1065万
 $24,485/呎
 (已售)</t>
         </is>
       </c>
-      <c r="H27" s="16" t="inlineStr">
+      <c r="H26" s="20" t="inlineStr">
         <is>
           <t>G | 462呎 (2房)
-$1,136万
+$1136万
 $24,600/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="65" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B28" s="16" t="inlineStr">
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B27" s="20" t="inlineStr">
         <is>
           <t>A | 525呎 (2房)
-$1,371万
+$1371万
 $26,120/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C28" s="16" t="inlineStr">
+      <c r="C27" s="20" t="inlineStr">
         <is>
           <t>B | 574呎 (3房)
-$1,554万
+$1554万
 $27,078/呎
 (24年-05月)</t>
         </is>
       </c>
-      <c r="D28" s="16" t="inlineStr">
+      <c r="D27" s="20" t="inlineStr">
         <is>
           <t>C | 457呎 (2房)
-$1,234万
+$1234万
 $26,998/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E28" s="16" t="inlineStr">
+      <c r="E27" s="20" t="inlineStr">
         <is>
           <t>D | 435呎 (2房)
-$1,144万
+$1144万
 $26,294/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F28" s="16" t="inlineStr">
+      <c r="F27" s="20" t="inlineStr">
         <is>
           <t>E | 450呎 (2房)
-$1,095万
+$1095万
 $24,342/呎
 (24年-04月)</t>
         </is>
       </c>
-      <c r="G28" s="16" t="inlineStr">
+      <c r="G27" s="20" t="inlineStr">
         <is>
           <t>F | 435呎 (2房)
-$1,044万
+$1044万
 $24,007/呎
 (23年-07月)</t>
         </is>
       </c>
-      <c r="H28" s="16" t="inlineStr">
+      <c r="H27" s="20" t="inlineStr">
         <is>
           <t>G | 462呎 (2房)
-$1,135万
+$1135万
 $24,574/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="65" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B29" s="16" t="inlineStr">
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B28" s="20" t="inlineStr">
         <is>
           <t>A | 525呎 (2房)
-$1,408万
+$1408万
 $26,829/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C29" s="16" t="inlineStr">
+      <c r="C28" s="20" t="inlineStr">
         <is>
           <t>B | 574呎 (3房)
-$1,545万
+$1545万
 $26,916/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D29" s="16" t="inlineStr">
+      <c r="D28" s="20" t="inlineStr">
         <is>
           <t>C | 457呎 (2房)
-$1,206万
+$1206万
 $26,392/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E29" s="16" t="inlineStr">
+      <c r="E28" s="20" t="inlineStr">
         <is>
           <t>D | 435呎 (2房)
-$1,142万
+$1142万
 $26,241/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F29" s="16" t="inlineStr">
+      <c r="F28" s="20" t="inlineStr">
         <is>
           <t>E | 450呎 (2房)
-$1,092万
+$1092万
 $24,271/呎
 (26年-02月)</t>
         </is>
       </c>
-      <c r="G29" s="16" t="inlineStr">
+      <c r="G28" s="20" t="inlineStr">
         <is>
           <t>F | 435呎 (2房)
-$1,059万
+$1059万
 $24,338/呎
 (已售)</t>
         </is>
       </c>
-      <c r="H29" s="16" t="inlineStr">
+      <c r="H28" s="20" t="inlineStr">
         <is>
           <t>G | 462呎 (2房)
-$1,134万
+$1134万
 $24,545/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="65" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B30" s="16" t="inlineStr">
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B29" s="20" t="inlineStr">
         <is>
           <t>A | 525呎 (2房)
-$1,401万
+$1401万
 $26,684/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C30" s="16" t="inlineStr">
+      <c r="C29" s="20" t="inlineStr">
         <is>
           <t>B | 574呎 (3房)
-$1,485万
+$1485万
 $25,875/呎
 (24年-04月)</t>
         </is>
       </c>
-      <c r="D30" s="16" t="inlineStr">
+      <c r="D29" s="20" t="inlineStr">
         <is>
           <t>C | 457呎 (2房)
-$1,180万
+$1180万
 $25,829/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E30" s="16" t="inlineStr">
+      <c r="E29" s="20" t="inlineStr">
         <is>
           <t>D | 435呎 (2房)
-$1,124万
+$1124万
 $25,844/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F30" s="16" t="inlineStr">
+      <c r="F29" s="20" t="inlineStr">
         <is>
           <t>E | 450呎 (2房)
-$1,089万
+$1089万
 $24,198/呎
 (26年-02月)</t>
         </is>
       </c>
-      <c r="G30" s="16" t="inlineStr">
+      <c r="G29" s="20" t="inlineStr">
         <is>
           <t>F | 435呎 (2房)
-$1,038万
+$1038万
 $23,864/呎
 (23年-11月)</t>
         </is>
       </c>
-      <c r="H30" s="16" t="inlineStr">
+      <c r="H29" s="20" t="inlineStr">
         <is>
           <t>G | 462呎 (2房)
-$1,133万
+$1133万
 $24,519/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="65" customHeight="1">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B31" s="16" t="inlineStr">
+    <row r="30" ht="58" customHeight="1">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B30" s="20" t="inlineStr">
         <is>
           <t>A | 525呎 (2房)
-$1,400万
+$1400万
 $26,669/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C31" s="16" t="inlineStr">
+      <c r="C30" s="20" t="inlineStr">
         <is>
           <t>B | 574呎 (3房)
-$1,472万
+$1472万
 $25,643/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D31" s="16" t="inlineStr">
+      <c r="D30" s="20" t="inlineStr">
         <is>
           <t>C | 457呎 (2房)
-$1,165万
+$1165万
 $25,499/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E31" s="16" t="inlineStr">
+      <c r="E30" s="20" t="inlineStr">
         <is>
           <t>D | 435呎 (2房)
-$1,100万
+$1100万
 $25,278/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F31" s="16" t="inlineStr">
+      <c r="F30" s="20" t="inlineStr">
         <is>
           <t>E | 450呎 (2房)
-$1,086万
+$1086万
 $24,124/呎
 (26年-02月)</t>
         </is>
       </c>
-      <c r="G31" s="16" t="inlineStr">
+      <c r="G30" s="20" t="inlineStr">
         <is>
           <t>F | 435呎 (2房)
-$1,035万
+$1035万
 $23,791/呎
 (24年-01月)</t>
         </is>
       </c>
-      <c r="H31" s="16" t="inlineStr">
+      <c r="H30" s="20" t="inlineStr">
         <is>
           <t>G | 462呎 (2房)
-$1,113万
+$1113万
 $24,087/呎
 (23年-12月)</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="65" customHeight="1">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B32" s="16" t="inlineStr">
+    <row r="31" ht="58" customHeight="1">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B31" s="20" t="inlineStr">
         <is>
           <t>A | 525呎 (2房)
-$1,376万
+$1376万
 $26,206/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C32" s="16" t="inlineStr">
+      <c r="C31" s="20" t="inlineStr">
         <is>
           <t>B | 574呎 (3房)
-$1,453万
+$1453万
 $25,310/呎
 (24年-04月)</t>
         </is>
       </c>
-      <c r="D32" s="16" t="inlineStr">
+      <c r="D31" s="20" t="inlineStr">
         <is>
           <t>C | 457呎 (2房)
-$1,150万
+$1150万
 $25,171/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E32" s="16" t="inlineStr">
+      <c r="E31" s="20" t="inlineStr">
         <is>
           <t>D | 435呎 (2房)
-$1,094万
+$1094万
 $25,138/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F32" s="16" t="inlineStr">
+      <c r="F31" s="20" t="inlineStr">
         <is>
           <t>E | 450呎 (2房)
-$1,082万
+$1082万
 $24,053/呎
 (25年-04月)</t>
         </is>
       </c>
-      <c r="G32" s="16" t="inlineStr">
+      <c r="G31" s="20" t="inlineStr">
         <is>
           <t>F | 435呎 (2房)
-$1,032万
+$1032万
 $23,720/呎
 (23年-12月)</t>
         </is>
       </c>
-      <c r="H32" s="16" t="inlineStr">
+      <c r="H31" s="20" t="inlineStr">
         <is>
           <t>G | 462呎 (2房)
-$1,112万
+$1112万
 $24,063/呎
 (24年-05月)</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="65" customHeight="1">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B33" s="16" t="inlineStr">
+    <row r="32" ht="58" customHeight="1">
+      <c r="A32" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B32" s="20" t="inlineStr">
         <is>
           <t>A | 525呎 (2房)
-$1,373万
+$1373万
 $26,158/呎
 (23年-12月)</t>
         </is>
       </c>
-      <c r="C33" s="16" t="inlineStr">
+      <c r="C32" s="20" t="inlineStr">
         <is>
           <t>B | 574呎 (3房)
-$1,432万
+$1432万
 $24,953/呎
 (24年-06月)</t>
         </is>
       </c>
-      <c r="D33" s="16" t="inlineStr">
+      <c r="D32" s="20" t="inlineStr">
         <is>
           <t>C | 457呎 (2房)
-$1,104万
+$1104万
 $24,162/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E33" s="16" t="inlineStr">
+      <c r="E32" s="20" t="inlineStr">
         <is>
           <t>D | 435呎 (2房)
-$1,085万
+$1085万
 $24,938/呎
 (23年-08月)</t>
         </is>
       </c>
-      <c r="F33" s="16" t="inlineStr">
+      <c r="F32" s="20" t="inlineStr">
         <is>
           <t>E | 450呎 (2房)
-$1,076万
+$1076万
 $23,909/呎
 (26年-03月)</t>
         </is>
       </c>
-      <c r="G33" s="16" t="inlineStr">
+      <c r="G32" s="20" t="inlineStr">
         <is>
           <t>F | 435呎 (2房)
-$1,026万
+$1026万
 $23,579/呎
 (24年-02月)</t>
         </is>
       </c>
-      <c r="H33" s="16" t="inlineStr">
+      <c r="H32" s="20" t="inlineStr">
         <is>
           <t>G | 462呎 (2房)
-$1,107万
+$1107万
 $23,963/呎
 (25年-11月)</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="65" customHeight="1">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B34" s="16" t="inlineStr">
+    <row r="33" ht="58" customHeight="1">
+      <c r="A33" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B33" s="20" t="inlineStr">
         <is>
           <t>A | 525呎 (2房)
-$1,373万
+$1373万
 $26,158/呎
 (24年-02月)</t>
         </is>
       </c>
-      <c r="C34" s="16" t="inlineStr">
+      <c r="C33" s="20" t="inlineStr">
         <is>
           <t>B | 574呎 (3房)
-$1,397万
+$1397万
 $24,338/呎
 (24年-04月)</t>
         </is>
       </c>
-      <c r="D34" s="16" t="inlineStr">
+      <c r="D33" s="20" t="inlineStr">
         <is>
           <t>C | 457呎 (2房)
-$1,078万
+$1078万
 $23,595/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E34" s="16" t="inlineStr">
+      <c r="E33" s="20" t="inlineStr">
         <is>
           <t>D | 435呎 (2房)
-$1,067万
+$1067万
 $24,531/呎
 (24年-01月)</t>
         </is>
       </c>
-      <c r="F34" s="16" t="inlineStr">
+      <c r="F33" s="20" t="inlineStr">
         <is>
           <t>E | 450呎 (2房)
-$1,073万
+$1073万
 $23,838/呎
 (26年-03月)</t>
         </is>
       </c>
-      <c r="G34" s="16" t="inlineStr">
+      <c r="G33" s="20" t="inlineStr">
         <is>
           <t>F | 435呎 (2房)
-$1,022万
+$1022万
 $23,503/呎
 (24年-04月)</t>
         </is>
       </c>
-      <c r="H34" s="16" t="inlineStr">
+      <c r="H33" s="20" t="inlineStr">
         <is>
           <t>G | 462呎 (2房)
-$1,106万
+$1106万
 $23,937/呎
 (26年-03月)</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="65" customHeight="1">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B35" s="16" t="inlineStr">
+    <row r="34" ht="58" customHeight="1">
+      <c r="A34" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B34" s="20" t="inlineStr">
         <is>
           <t>A | 524呎 (2房)
-$1,357万
+$1357万
 $25,895/呎
 (24年-02月)</t>
         </is>
       </c>
-      <c r="C35" s="16" t="inlineStr">
+      <c r="C34" s="20" t="inlineStr">
         <is>
           <t>B | 574呎 (3房)
-$1,393万
+$1393万
 $24,267/呎
 (25年-08月)</t>
         </is>
       </c>
-      <c r="D35" s="16" t="inlineStr">
+      <c r="D34" s="20" t="inlineStr">
         <is>
           <t>C | 457呎 (2房)
-$1,106万
+$1106万
 $24,193/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E35" s="16" t="inlineStr">
+      <c r="E34" s="20" t="inlineStr">
         <is>
           <t>D | 435呎 (2房)
-$1,066万
+$1066万
 $24,515/呎
 (23年-12月)</t>
         </is>
       </c>
-      <c r="F35" s="16" t="inlineStr">
+      <c r="F34" s="20" t="inlineStr">
         <is>
           <t>E | 450呎 (2房)
-$1,070万
+$1070万
 $23,767/呎
 (26年-03月)</t>
         </is>
       </c>
-      <c r="G35" s="16" t="inlineStr">
+      <c r="G34" s="20" t="inlineStr">
         <is>
           <t>F | 435呎 (2房)
-$1,019万
+$1019万
 $23,434/呎
 (24年-05月)</t>
         </is>
       </c>
-      <c r="H35" s="16" t="inlineStr">
+      <c r="H34" s="20" t="inlineStr">
         <is>
           <t>G | 462呎 (2房)
-$1,103万
+$1103万
 $23,866/呎
 (26年-03月)</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="65" customHeight="1">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B36" s="16" t="inlineStr">
+    <row r="35" ht="58" customHeight="1">
+      <c r="A35" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B35" s="20" t="inlineStr">
         <is>
           <t>A | 524呎 (2房)
-$1,347万
+$1347万
 $25,700/呎
 (24年-05月)</t>
         </is>
       </c>
-      <c r="C36" s="16" t="inlineStr">
+      <c r="C35" s="20" t="inlineStr">
         <is>
           <t>B | 574呎 (3房)
-$1,319万
+$1319万
 $22,984/呎
 (25年-10月)</t>
         </is>
       </c>
-      <c r="D36" s="16" t="inlineStr">
+      <c r="D35" s="20" t="inlineStr">
         <is>
           <t>C | 457呎 (2房)
-$1,102万
+$1102万
 $24,120/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E36" s="16" t="inlineStr">
+      <c r="E35" s="20" t="inlineStr">
         <is>
           <t>D | 435呎 (2房)
-$1,040万
+$1040万
 $23,901/呎
 (24年-04月)</t>
         </is>
       </c>
-      <c r="F36" s="16" t="inlineStr">
+      <c r="F35" s="20" t="inlineStr">
         <is>
           <t>E | 450呎 (2房)
-$1,090万
+$1090万
 $24,227/呎
 (26年-03月)</t>
         </is>
       </c>
-      <c r="G36" s="16" t="inlineStr">
+      <c r="G35" s="20" t="inlineStr">
         <is>
           <t>F | 356呎 (1房)
 $893万
@@ -30746,11 +30784,11 @@
 (26年-05月)</t>
         </is>
       </c>
-      <c r="H36" s="17" t="inlineStr"/>
+      <c r="H35" s="21" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -30763,339 +30801,339 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Monaco Marine - 低座A 销控网格图</t>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>低座A 销控网格图</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>总套数</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="8" t="inlineStr">
         <is>
           <t>在售 (Sale)</t>
         </is>
       </c>
-      <c r="C2" s="8" t="inlineStr">
+      <c r="C2" s="9" t="inlineStr">
         <is>
           <t>已定价未售</t>
         </is>
       </c>
-      <c r="D2" s="9" t="inlineStr">
+      <c r="D2" s="10" t="inlineStr">
         <is>
           <t>已售 (Sold)</t>
         </is>
       </c>
-      <c r="E2" s="10" t="inlineStr">
+      <c r="E2" s="11" t="inlineStr">
         <is>
           <t>暂停销售</t>
         </is>
       </c>
-      <c r="F2" s="6" t="inlineStr">
+      <c r="F2" s="12" t="inlineStr">
         <is>
           <t>待售 (Pending)</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>24 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>24 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C4" s="19" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D4" s="19" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E4" s="19" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F4" s="19" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
         <is>
           <t>A | 595呎 (3房)
-$1,516万
+$1516万
 $25,482/呎
 (24年-03月)</t>
         </is>
       </c>
-      <c r="C6" s="16" t="inlineStr">
+      <c r="C5" s="20" t="inlineStr">
         <is>
           <t>B | 601呎 (3房)
-$1,636万
+$1636万
 $27,220/呎
 (24年-02月)</t>
         </is>
       </c>
-      <c r="D6" s="16" t="inlineStr">
+      <c r="D5" s="20" t="inlineStr">
         <is>
           <t>C | 767呎 (3房)
-$2,092万
+$2092万
 $27,280/呎
 (23年-08月)</t>
         </is>
       </c>
-      <c r="E6" s="16" t="inlineStr">
+      <c r="E5" s="20" t="inlineStr">
         <is>
           <t>D | 448呎 (2房)
-$1,120万
+$1120万
 $25,009/呎
 (24年-05月)</t>
         </is>
       </c>
-      <c r="F6" s="16" t="inlineStr">
+      <c r="F5" s="20" t="inlineStr">
         <is>
           <t>E | 453呎 (2房)
-$1,166万
+$1166万
 $25,737/呎
 (23年-12月)</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
         <is>
           <t>A | 596呎 (3房)
-$1,507万
+$1507万
 $25,287/呎
 (24年-03月)</t>
         </is>
       </c>
-      <c r="C7" s="16" t="inlineStr">
+      <c r="C6" s="20" t="inlineStr">
         <is>
           <t>B | 601呎 (3房)
-$1,511万
+$1511万
 $25,148/呎
 (24年-04月)</t>
         </is>
       </c>
-      <c r="D7" s="16" t="inlineStr">
+      <c r="D6" s="20" t="inlineStr">
         <is>
           <t>C | 767呎 (3房)
-$1,918万
+$1918万
 $25,007/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E7" s="16" t="inlineStr">
+      <c r="E6" s="20" t="inlineStr">
         <is>
           <t>D | 448呎 (2房)
-$1,114万
+$1114万
 $24,859/呎
 (25年-08月)</t>
         </is>
       </c>
-      <c r="F7" s="16" t="inlineStr">
+      <c r="F6" s="20" t="inlineStr">
         <is>
           <t>E | 453呎 (2房)
-$1,159万
+$1159万
 $25,585/呎
 (23年-12月)</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>2/F</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="inlineStr">
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
         <is>
           <t>A | 595呎 (3房)
-$1,498万
+$1498万
 $25,178/呎
 (24年-04月)</t>
         </is>
       </c>
-      <c r="C8" s="16" t="inlineStr">
+      <c r="C7" s="20" t="inlineStr">
         <is>
           <t>B | 601呎 (3房)
-$1,502万
+$1502万
 $24,998/呎
 (24年-04月)</t>
         </is>
       </c>
-      <c r="D8" s="16" t="inlineStr">
+      <c r="D7" s="20" t="inlineStr">
         <is>
           <t>C | 768呎 (3房)
-$1,916万
+$1916万
 $24,949/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E8" s="16" t="inlineStr">
+      <c r="E7" s="20" t="inlineStr">
         <is>
           <t>D | 448呎 (2房)
-$1,107万
+$1107万
 $24,710/呎
 (25年-11月)</t>
         </is>
       </c>
-      <c r="F8" s="16" t="inlineStr">
+      <c r="F7" s="20" t="inlineStr">
         <is>
           <t>E | 453呎 (2房)
-$1,152万
+$1152万
 $25,433/呎
 (23年-12月)</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>1/F</t>
-        </is>
-      </c>
-      <c r="B9" s="16" t="inlineStr">
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
         <is>
           <t>A | 595呎 (3房)
-$1,489万
+$1489万
 $25,029/呎
 (24年-04月)</t>
         </is>
       </c>
-      <c r="C9" s="16" t="inlineStr">
+      <c r="C8" s="20" t="inlineStr">
         <is>
           <t>B | 601呎 (3房)
-$1,493万
+$1493万
 $24,849/呎
 (24年-05月)</t>
         </is>
       </c>
-      <c r="D9" s="16" t="inlineStr">
+      <c r="D8" s="20" t="inlineStr">
         <is>
           <t>C | 768呎 (3房)
-$1,873万
+$1873万
 $24,389/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E9" s="16" t="inlineStr">
+      <c r="E8" s="20" t="inlineStr">
         <is>
           <t>D | 448呎 (2房)
-$1,100万
+$1100万
 $24,562/呎
 (25年-04月)</t>
         </is>
       </c>
-      <c r="F9" s="16" t="inlineStr">
+      <c r="F8" s="20" t="inlineStr">
         <is>
           <t>E | 453呎 (2房)
-$1,145万
+$1145万
 $25,280/呎
 (24年-04月)</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>G/F</t>
-        </is>
-      </c>
-      <c r="B10" s="16" t="inlineStr">
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
         <is>
           <t>A | 579呎 (3房)
-$1,719万
+$1719万
 $29,684/呎
 (23年-12月)</t>
         </is>
       </c>
-      <c r="C10" s="16" t="inlineStr">
+      <c r="C9" s="20" t="inlineStr">
         <is>
           <t>B | 578呎 (3房)
-$1,618万
+$1618万
 $27,993/呎
 (23年-12月)</t>
         </is>
       </c>
-      <c r="D10" s="16" t="inlineStr">
+      <c r="D9" s="20" t="inlineStr">
         <is>
           <t>C | 741呎 (3房)
-$1,991万
+$1991万
 $26,865/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E10" s="16" t="inlineStr">
+      <c r="E9" s="20" t="inlineStr">
         <is>
           <t>D | 343呎 (1房)
 $985万
@@ -31103,7 +31141,7 @@
 (24年-04月)</t>
         </is>
       </c>
-      <c r="F10" s="17" t="inlineStr"/>
+      <c r="F9" s="21" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -31120,143 +31158,143 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Monaco Marine - 低座B 销控网格图</t>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>低座B 销控网格图</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>总套数</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="8" t="inlineStr">
         <is>
           <t>在售 (Sale)</t>
         </is>
       </c>
-      <c r="C2" s="8" t="inlineStr">
+      <c r="C2" s="9" t="inlineStr">
         <is>
           <t>已定价未售</t>
         </is>
       </c>
-      <c r="D2" s="9" t="inlineStr">
+      <c r="D2" s="10" t="inlineStr">
         <is>
           <t>已售 (Sold)</t>
         </is>
       </c>
-      <c r="E2" s="10" t="inlineStr">
+      <c r="E2" s="11" t="inlineStr">
         <is>
           <t>暂停销售</t>
         </is>
       </c>
-      <c r="F2" s="6" t="inlineStr">
+      <c r="F2" s="12" t="inlineStr">
         <is>
           <t>待售 (Pending)</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>28 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>1 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>27 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C4" s="19" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D4" s="19" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E4" s="19" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F4" s="19" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
         <is>
           <t>A | 720呎 (3房)
-$1,933万
+$1933万
 $26,847/呎
 (23年-08月)</t>
         </is>
       </c>
-      <c r="C6" s="16" t="inlineStr">
+      <c r="C5" s="20" t="inlineStr">
         <is>
           <t>B | 425呎 (2房)
-$1,261万
+$1261万
 $29,678/呎
 (23年-07月)</t>
         </is>
       </c>
-      <c r="D6" s="16" t="inlineStr">
+      <c r="D5" s="20" t="inlineStr">
         <is>
           <t>C | 324呎 (1房)
 $873万
@@ -31264,7 +31302,7 @@
 (24年-05月)</t>
         </is>
       </c>
-      <c r="E6" s="16" t="inlineStr">
+      <c r="E5" s="20" t="inlineStr">
         <is>
           <t>D | 337呎 (1房)
 $907万
@@ -31272,38 +31310,38 @@
 (26年-04月)</t>
         </is>
       </c>
-      <c r="F6" s="16" t="inlineStr">
+      <c r="F5" s="20" t="inlineStr">
         <is>
           <t>E | 453呎 (2房)
-$1,156万
+$1156万
 $25,525/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
         <is>
           <t>A | 720呎 (3房)
-$1,822万
+$1822万
 $25,307/呎
 (23年-07月)</t>
         </is>
       </c>
-      <c r="C7" s="16" t="inlineStr">
+      <c r="C6" s="20" t="inlineStr">
         <is>
           <t>B | 425呎 (2房)
-$1,103万
+$1103万
 $25,951/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D7" s="16" t="inlineStr">
+      <c r="D6" s="20" t="inlineStr">
         <is>
           <t>C | 324呎 (1房)
 $868万
@@ -31311,7 +31349,7 @@
 (24年-04月)</t>
         </is>
       </c>
-      <c r="E7" s="16" t="inlineStr">
+      <c r="E6" s="20" t="inlineStr">
         <is>
           <t>D | 337呎 (1房)
 $906万
@@ -31319,38 +31357,38 @@
 (26年-04月)</t>
         </is>
       </c>
-      <c r="F7" s="16" t="inlineStr">
+      <c r="F6" s="20" t="inlineStr">
         <is>
           <t>E | 453呎 (2房)
-$1,149万
+$1149万
 $25,373/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="inlineStr">
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
         <is>
           <t>A | 720呎 (3房)
-$1,811万
+$1811万
 $25,156/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C8" s="16" t="inlineStr">
+      <c r="C7" s="20" t="inlineStr">
         <is>
           <t>B | 425呎 (2房)
-$1,096万
+$1096万
 $25,795/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D8" s="16" t="inlineStr">
+      <c r="D7" s="20" t="inlineStr">
         <is>
           <t>C | 324呎 (1房)
 $862万
@@ -31358,7 +31396,7 @@
 (24年-06月)</t>
         </is>
       </c>
-      <c r="E8" s="16" t="inlineStr">
+      <c r="E7" s="20" t="inlineStr">
         <is>
           <t>D | 337呎 (1房)
 $885万
@@ -31366,38 +31404,38 @@
 (24年-06月)</t>
         </is>
       </c>
-      <c r="F8" s="16" t="inlineStr">
+      <c r="F7" s="20" t="inlineStr">
         <is>
           <t>E | 453呎 (2房)
-$1,142万
+$1142万
 $25,221/呎
 (23年-11月)</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>2/F</t>
-        </is>
-      </c>
-      <c r="B9" s="16" t="inlineStr">
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
         <is>
           <t>A | 720呎 (3房)
-$1,800万
+$1800万
 $25,006/呎
 (23年-07月)</t>
         </is>
       </c>
-      <c r="C9" s="16" t="inlineStr">
+      <c r="C8" s="20" t="inlineStr">
         <is>
           <t>B | 425呎 (2房)
-$1,072万
+$1072万
 $25,216/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D9" s="16" t="inlineStr">
+      <c r="D8" s="20" t="inlineStr">
         <is>
           <t>C | 324呎 (1房)
 $857万
@@ -31405,7 +31443,7 @@
 (24年-05月)</t>
         </is>
       </c>
-      <c r="E9" s="16" t="inlineStr">
+      <c r="E8" s="20" t="inlineStr">
         <is>
           <t>D | 337呎 (1房)
 $899万
@@ -31413,38 +31451,38 @@
 (26年-05月)</t>
         </is>
       </c>
-      <c r="F9" s="16" t="inlineStr">
+      <c r="F8" s="20" t="inlineStr">
         <is>
           <t>E | 453呎 (2房)
-$1,136万
+$1136万
 $25,071/呎
 (24年-04月)</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>1/F</t>
-        </is>
-      </c>
-      <c r="B10" s="16" t="inlineStr">
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
         <is>
           <t>A | 720呎 (3房)
-$1,790万
+$1790万
 $24,857/呎
 (23年-12月)</t>
         </is>
       </c>
-      <c r="C10" s="16" t="inlineStr">
+      <c r="C9" s="20" t="inlineStr">
         <is>
           <t>B | 425呎 (2房)
-$1,059万
+$1059万
 $24,925/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D10" s="16" t="inlineStr">
+      <c r="D9" s="20" t="inlineStr">
         <is>
           <t>C | 324呎 (1房)
 $871万
@@ -31452,7 +31490,7 @@
 (26年-06月)</t>
         </is>
       </c>
-      <c r="E10" s="18" t="inlineStr">
+      <c r="E9" s="22" t="inlineStr">
         <is>
           <t>D | 337呎 (1房)
 $982万
@@ -31460,47 +31498,47 @@
 (在售)</t>
         </is>
       </c>
-      <c r="F10" s="16" t="inlineStr">
+      <c r="F9" s="20" t="inlineStr">
         <is>
           <t>E | 453呎 (2房)
-$1,129万
+$1129万
 $24,921/呎
 (24年-04月)</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>G/F</t>
-        </is>
-      </c>
-      <c r="B11" s="16" t="inlineStr">
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
         <is>
           <t>A | 696呎 (3房)
-$2,000万
+$2000万
 $28,736/呎
 (23年-08月)</t>
         </is>
       </c>
-      <c r="C11" s="16" t="inlineStr">
+      <c r="C10" s="20" t="inlineStr">
         <is>
           <t>B | 409呎 (2房)
-$1,184万
+$1184万
 $28,956/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D11" s="16" t="inlineStr">
+      <c r="D10" s="20" t="inlineStr">
         <is>
           <t>C | 625呎 (2房)
-$1,876万
+$1876万
 $30,022/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E11" s="17" t="inlineStr"/>
-      <c r="F11" s="17" t="inlineStr"/>
+      <c r="E10" s="21" t="inlineStr"/>
+      <c r="F10" s="21" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -31517,390 +31555,390 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Monaco Marine - 低座C 销控网格图</t>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>低座C 销控网格图</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>总套数</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="8" t="inlineStr">
         <is>
           <t>在售 (Sale)</t>
         </is>
       </c>
-      <c r="C2" s="8" t="inlineStr">
+      <c r="C2" s="9" t="inlineStr">
         <is>
           <t>已定价未售</t>
         </is>
       </c>
-      <c r="D2" s="9" t="inlineStr">
+      <c r="D2" s="10" t="inlineStr">
         <is>
           <t>已售 (Sold)</t>
         </is>
       </c>
-      <c r="E2" s="10" t="inlineStr">
+      <c r="E2" s="11" t="inlineStr">
         <is>
           <t>暂停销售</t>
         </is>
       </c>
-      <c r="F2" s="6" t="inlineStr">
+      <c r="F2" s="12" t="inlineStr">
         <is>
           <t>待售 (Pending)</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>28 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>28 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C4" s="19" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D4" s="19" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E4" s="19" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F4" s="19" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G4" s="19" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
         <is>
           <t>A | 717呎 (3房)
-$1,814万
+$1814万
 $25,307/呎
 (23年-11月)</t>
         </is>
       </c>
-      <c r="C6" s="16" t="inlineStr">
+      <c r="C5" s="20" t="inlineStr">
         <is>
           <t>B | 597呎 (3房)
-$1,780万
+$1780万
 $29,816/呎
 (24年-04月)</t>
         </is>
       </c>
-      <c r="D6" s="16" t="inlineStr">
+      <c r="D5" s="20" t="inlineStr">
         <is>
           <t>C | 566呎 (3房)
-$1,696万
+$1696万
 $29,961/呎
 (24年-05月)</t>
         </is>
       </c>
-      <c r="E6" s="16" t="inlineStr">
+      <c r="E5" s="20" t="inlineStr">
         <is>
           <t>D | 457呎 (2房)
-$1,137万
+$1137万
 $24,886/呎
 (24年-05月)</t>
         </is>
       </c>
-      <c r="F6" s="16" t="inlineStr">
+      <c r="F5" s="20" t="inlineStr">
         <is>
           <t>E | 440呎 (2房)
-$1,101万
+$1101万
 $25,032/呎
 (24年-04月)</t>
         </is>
       </c>
-      <c r="G6" s="16" t="inlineStr">
+      <c r="G5" s="20" t="inlineStr">
         <is>
           <t>F | 446呎 (2房)
-$1,132万
+$1132万
 $25,372/呎
 (24年-01月)</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
         <is>
           <t>A | 717呎 (3房)
-$1,818万
+$1818万
 $25,349/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C7" s="16" t="inlineStr">
+      <c r="C6" s="20" t="inlineStr">
         <is>
           <t>B | 597呎 (3房)
-$1,509万
+$1509万
 $25,275/呎
 (23年-11月)</t>
         </is>
       </c>
-      <c r="D7" s="16" t="inlineStr">
+      <c r="D6" s="20" t="inlineStr">
         <is>
           <t>C | 566呎 (3房)
-$1,441万
+$1441万
 $25,458/呎
 (24年-02月)</t>
         </is>
       </c>
-      <c r="E7" s="16" t="inlineStr">
+      <c r="E6" s="20" t="inlineStr">
         <is>
           <t>D | 456呎 (2房)
-$1,130万
+$1130万
 $24,792/呎
 (25年-05月)</t>
         </is>
       </c>
-      <c r="F7" s="16" t="inlineStr">
+      <c r="F6" s="20" t="inlineStr">
         <is>
           <t>E | 440呎 (2房)
-$1,095万
+$1095万
 $24,882/呎
 (24年-04月)</t>
         </is>
       </c>
-      <c r="G7" s="16" t="inlineStr">
+      <c r="G6" s="20" t="inlineStr">
         <is>
           <t>F | 446呎 (2房)
-$1,125万
+$1125万
 $25,222/呎
 (24年-04月)</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>2/F</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="inlineStr">
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
         <is>
           <t>A | 717呎 (3房)
-$1,777万
+$1777万
 $24,780/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C8" s="16" t="inlineStr">
+      <c r="C7" s="20" t="inlineStr">
         <is>
           <t>B | 597呎 (3房)
-$1,500万
+$1500万
 $25,124/呎
 (24年-04月)</t>
         </is>
       </c>
-      <c r="D8" s="16" t="inlineStr">
+      <c r="D7" s="20" t="inlineStr">
         <is>
           <t>C | 566呎 (3房)
-$1,432万
+$1432万
 $25,306/呎
 (24年-04月)</t>
         </is>
       </c>
-      <c r="E8" s="16" t="inlineStr">
+      <c r="E7" s="20" t="inlineStr">
         <is>
           <t>D | 456呎 (2房)
-$1,124万
+$1124万
 $24,645/呎
 (25年-09月)</t>
         </is>
       </c>
-      <c r="F8" s="16" t="inlineStr">
+      <c r="F7" s="20" t="inlineStr">
         <is>
           <t>E | 440呎 (2房)
-$1,088万
+$1088万
 $24,734/呎
 (24年-05月)</t>
         </is>
       </c>
-      <c r="G8" s="16" t="inlineStr">
+      <c r="G7" s="20" t="inlineStr">
         <is>
           <t>F | 446呎 (2房)
-$1,118万
+$1118万
 $25,072/呎
 (24年-04月)</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>1/F</t>
-        </is>
-      </c>
-      <c r="B9" s="16" t="inlineStr">
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
         <is>
           <t>A | 717呎 (3房)
-$1,766万
+$1766万
 $24,632/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C9" s="16" t="inlineStr">
+      <c r="C8" s="20" t="inlineStr">
         <is>
           <t>B | 597呎 (3房)
-$1,491万
+$1491万
 $24,975/呎
 (24年-04月)</t>
         </is>
       </c>
-      <c r="D9" s="16" t="inlineStr">
+      <c r="D8" s="20" t="inlineStr">
         <is>
           <t>C | 566呎 (3房)
-$1,514万
+$1514万
 $26,746/呎
 (25年-02月)</t>
         </is>
       </c>
-      <c r="E9" s="16" t="inlineStr">
+      <c r="E8" s="20" t="inlineStr">
         <is>
           <t>D | 456呎 (2房)
-$1,117万
+$1117万
 $24,498/呎
 (25年-11月)</t>
         </is>
       </c>
-      <c r="F9" s="16" t="inlineStr">
+      <c r="F8" s="20" t="inlineStr">
         <is>
           <t>E | 440呎 (2房)
-$1,082万
+$1082万
 $24,586/呎
 (24年-05月)</t>
         </is>
       </c>
-      <c r="G9" s="16" t="inlineStr">
+      <c r="G8" s="20" t="inlineStr">
         <is>
           <t>F | 446呎 (2房)
-$1,112万
+$1112万
 $24,922/呎
 (25年-10月)</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>G/F</t>
-        </is>
-      </c>
-      <c r="B10" s="16" t="inlineStr">
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
         <is>
           <t>A | 703呎 (3房)
-$2,028万
+$2028万
 $28,848/呎
 (23年-11月)</t>
         </is>
       </c>
-      <c r="C10" s="16" t="inlineStr">
+      <c r="C9" s="20" t="inlineStr">
         <is>
           <t>B | 575呎 (3房)
-$1,619万
+$1619万
 $28,151/呎
 (23年-12月)</t>
         </is>
       </c>
-      <c r="D10" s="16" t="inlineStr">
+      <c r="D9" s="20" t="inlineStr">
         <is>
           <t>C | 529呎 (3房)
-$1,595万
+$1595万
 $30,144/呎
 (24年-01月)</t>
         </is>
       </c>
-      <c r="E10" s="16" t="inlineStr">
+      <c r="E9" s="20" t="inlineStr">
         <is>
           <t>D | 499呎 (3房)
-$1,464万
+$1464万
 $29,347/呎
 (23年-11月)</t>
         </is>
       </c>
-      <c r="F10" s="17" t="inlineStr"/>
-      <c r="G10" s="17" t="inlineStr"/>
+      <c r="F9" s="21" t="inlineStr"/>
+      <c r="G9" s="21" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -31913,143 +31951,143 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Monaco Marine - 低座D 销控网格图</t>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>低座D 销控网格图</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>总套数</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="8" t="inlineStr">
         <is>
           <t>在售 (Sale)</t>
         </is>
       </c>
-      <c r="C2" s="8" t="inlineStr">
+      <c r="C2" s="9" t="inlineStr">
         <is>
           <t>已定价未售</t>
         </is>
       </c>
-      <c r="D2" s="9" t="inlineStr">
+      <c r="D2" s="10" t="inlineStr">
         <is>
           <t>已售 (Sold)</t>
         </is>
       </c>
-      <c r="E2" s="10" t="inlineStr">
+      <c r="E2" s="11" t="inlineStr">
         <is>
           <t>暂停销售</t>
         </is>
       </c>
-      <c r="F2" s="6" t="inlineStr">
+      <c r="F2" s="12" t="inlineStr">
         <is>
           <t>待售 (Pending)</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>26 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>26 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C4" s="19" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D4" s="19" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E4" s="19" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F4" s="19" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
         <is>
           <t>A | 728呎 (3房)
-$1,960万
+$1960万
 $26,923/呎
 (23年-12月)</t>
         </is>
       </c>
-      <c r="C6" s="16" t="inlineStr">
+      <c r="C5" s="20" t="inlineStr">
         <is>
           <t>B | 446呎 (2房)
-$1,256万
+$1256万
 $28,173/呎
 (24年-01月)</t>
         </is>
       </c>
-      <c r="D6" s="16" t="inlineStr">
+      <c r="D5" s="20" t="inlineStr">
         <is>
           <t>C | 338呎 (1房)
 $886万
@@ -32057,39 +32095,39 @@
 (26年-03月)</t>
         </is>
       </c>
-      <c r="E6" s="17" t="inlineStr"/>
-      <c r="F6" s="16" t="inlineStr">
+      <c r="E5" s="21" t="inlineStr"/>
+      <c r="F5" s="20" t="inlineStr">
         <is>
           <t>E | 487呎 (2房)
-$1,180万
+$1180万
 $24,226/呎
 (24年-04月)</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
         <is>
           <t>A | 728呎 (3房)
-$1,834万
+$1834万
 $25,185/呎
 (23年-07月)</t>
         </is>
       </c>
-      <c r="C7" s="16" t="inlineStr">
+      <c r="C6" s="20" t="inlineStr">
         <is>
           <t>B | 446呎 (2房)
-$1,133万
+$1133万
 $25,399/呎
 (24年-04月)</t>
         </is>
       </c>
-      <c r="D7" s="16" t="inlineStr">
+      <c r="D6" s="20" t="inlineStr">
         <is>
           <t>C | 338呎 (1房)
 $880万
@@ -32097,39 +32135,39 @@
 (25年-04月)</t>
         </is>
       </c>
-      <c r="E7" s="17" t="inlineStr"/>
-      <c r="F7" s="16" t="inlineStr">
+      <c r="E6" s="21" t="inlineStr"/>
+      <c r="F6" s="20" t="inlineStr">
         <is>
           <t>E | 487呎 (2房)
-$1,179万
+$1179万
 $24,205/呎
 (24年-04月)</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="inlineStr">
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
         <is>
           <t>A | 728呎 (3房)
-$1,823万
+$1823万
 $25,036/呎
 (23年-12月)</t>
         </is>
       </c>
-      <c r="C8" s="16" t="inlineStr">
+      <c r="C7" s="20" t="inlineStr">
         <is>
           <t>B | 446呎 (2房)
-$1,126万
+$1126万
 $25,247/呎
 (24年-04月)</t>
         </is>
       </c>
-      <c r="D8" s="16" t="inlineStr">
+      <c r="D7" s="20" t="inlineStr">
         <is>
           <t>C | 333呎 (1房)
 $862万
@@ -32137,7 +32175,7 @@
 (24年-07月)</t>
         </is>
       </c>
-      <c r="E8" s="16" t="inlineStr">
+      <c r="E7" s="20" t="inlineStr">
         <is>
           <t>D | 361呎 (1房)
 $883万
@@ -32145,38 +32183,38 @@
 (24年-04月)</t>
         </is>
       </c>
-      <c r="F8" s="16" t="inlineStr">
+      <c r="F7" s="20" t="inlineStr">
         <is>
           <t>E | 487呎 (2房)
-$1,178万
+$1178万
 $24,181/呎
 (24年-04月)</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>2/F</t>
-        </is>
-      </c>
-      <c r="B9" s="16" t="inlineStr">
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
         <is>
           <t>A | 728呎 (3房)
-$1,812万
+$1812万
 $24,886/呎
 (23年-12月)</t>
         </is>
       </c>
-      <c r="C9" s="16" t="inlineStr">
+      <c r="C8" s="20" t="inlineStr">
         <is>
           <t>B | 446呎 (2房)
-$1,119万
+$1119万
 $25,094/呎
 (24年-04月)</t>
         </is>
       </c>
-      <c r="D9" s="16" t="inlineStr">
+      <c r="D8" s="20" t="inlineStr">
         <is>
           <t>C | 333呎 (1房)
 $857万
@@ -32184,7 +32222,7 @@
 (26年-01月)</t>
         </is>
       </c>
-      <c r="E9" s="16" t="inlineStr">
+      <c r="E8" s="20" t="inlineStr">
         <is>
           <t>D | 361呎 (1房)
 $882万
@@ -32192,38 +32230,38 @@
 (25年-01月)</t>
         </is>
       </c>
-      <c r="F9" s="16" t="inlineStr">
+      <c r="F8" s="20" t="inlineStr">
         <is>
           <t>E | 487呎 (2房)
-$1,176万
+$1176万
 $24,158/呎
 (24年-04月)</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>1/F</t>
-        </is>
-      </c>
-      <c r="B10" s="16" t="inlineStr">
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
         <is>
           <t>A | 728呎 (3房)
-$1,801万
+$1801万
 $24,743/呎
 (23年-12月)</t>
         </is>
       </c>
-      <c r="C10" s="16" t="inlineStr">
+      <c r="C9" s="20" t="inlineStr">
         <is>
           <t>B | 446呎 (2房)
-$1,112万
+$1112万
 $24,944/呎
 (24年-04月)</t>
         </is>
       </c>
-      <c r="D10" s="16" t="inlineStr">
+      <c r="D9" s="20" t="inlineStr">
         <is>
           <t>C | 333呎 (1房)
 $852万
@@ -32231,7 +32269,7 @@
 (26年-03月)</t>
         </is>
       </c>
-      <c r="E10" s="16" t="inlineStr">
+      <c r="E9" s="20" t="inlineStr">
         <is>
           <t>D | 361呎 (1房)
 $880万
@@ -32239,47 +32277,47 @@
 (26年-01月)</t>
         </is>
       </c>
-      <c r="F10" s="16" t="inlineStr">
+      <c r="F9" s="20" t="inlineStr">
         <is>
           <t>E | 487呎 (2房)
-$1,175万
+$1175万
 $24,133/呎
 (24年-07月)</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>G/F</t>
-        </is>
-      </c>
-      <c r="B11" s="16" t="inlineStr">
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
         <is>
           <t>A | 700呎 (3房)
-$1,947万
+$1947万
 $27,814/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C11" s="16" t="inlineStr">
+      <c r="C10" s="20" t="inlineStr">
         <is>
           <t>B | 425呎 (2房)
-$1,195万
+$1195万
 $28,127/呎
 (23年-12月)</t>
         </is>
       </c>
-      <c r="D11" s="16" t="inlineStr">
+      <c r="D10" s="20" t="inlineStr">
         <is>
           <t>C | 639呎 (2房)
-$1,794万
+$1794万
 $28,081/呎
 (24年-01月)</t>
         </is>
       </c>
-      <c r="E11" s="17" t="inlineStr"/>
-      <c r="F11" s="17" t="inlineStr"/>
+      <c r="E10" s="21" t="inlineStr"/>
+      <c r="F10" s="21" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
